--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU20"/>
+  <dimension ref="A1:AU32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,27 +588,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Amal Tiznit</t>
         </is>
       </c>
       <c r="G2">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -680,10 +680,10 @@
         <v>0</v>
       </c>
       <c r="AC2">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-10-02 14:00:00</t>
+          <t>2026-10-02 13:00:00</t>
         </is>
       </c>
     </row>
@@ -751,27 +751,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G3">
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-10-02 15:45:00</t>
+          <t>2026-10-02 14:00:00</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G4">
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1006,10 +1006,10 @@
         <v>0</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE4">
         <v>0</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-10-02 15:45:00</t>
+          <t>2026-10-02 14:00:00</t>
         </is>
       </c>
     </row>
@@ -1077,27 +1077,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Widad Témara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-10-02 15:45:00</t>
+          <t>2026-10-02 15:00:00</t>
         </is>
       </c>
     </row>
@@ -1240,27 +1240,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G6">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-10-02 15:45:00</t>
+          <t>2026-10-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1566,27 +1566,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-10-02 16:00:00</t>
+          <t>2026-10-02 15:45:00</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-10-02 19:30:00</t>
+          <t>2026-10-02 15:45:00</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-10-02 20:30:00</t>
+          <t>2026-10-02 15:45:00</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-10-02 20:45:00</t>
+          <t>2026-10-02 15:45:00</t>
         </is>
       </c>
     </row>
@@ -2218,27 +2218,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-10-02 21:00:00</t>
+          <t>2026-10-02 15:45:00</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-10-02 21:00:00</t>
+          <t>2026-10-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Moghreb Tétouan</t>
         </is>
       </c>
       <c r="G14">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-10-02 21:00:00</t>
+          <t>2026-10-02 17:00:00</t>
         </is>
       </c>
     </row>
@@ -2707,27 +2707,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-10-02 21:00:00</t>
+          <t>2026-10-02 19:30:00</t>
         </is>
       </c>
     </row>
@@ -2870,27 +2870,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-10-02 21:00:00</t>
+          <t>2026-10-02 20:00:00</t>
         </is>
       </c>
     </row>
@@ -3033,27 +3033,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-10-02 21:00:00</t>
+          <t>2026-10-02 20:00:00</t>
         </is>
       </c>
     </row>
@@ -3196,27 +3196,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G18">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-10-02 21:00:00</t>
+          <t>2026-10-02 20:30:00</t>
         </is>
       </c>
     </row>
@@ -3359,27 +3359,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G19">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-10-02 21:00:00</t>
+          <t>2026-10-02 20:45:00</t>
         </is>
       </c>
     </row>
@@ -3522,158 +3522,2114 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Ferro Carril Oeste</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-1</v>
+      </c>
+      <c r="AN20">
+        <v>-1</v>
+      </c>
+      <c r="AO20">
+        <v>-1</v>
+      </c>
+      <c r="AP20">
+        <v>-1</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2026-10-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Nueva Chicago</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Deportivo Maipú</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>-1</v>
+      </c>
+      <c r="AN21">
+        <v>-1</v>
+      </c>
+      <c r="AO21">
+        <v>-1</v>
+      </c>
+      <c r="AP21">
+        <v>-1</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2026-10-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Orlando Pride</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>San Diego Wave</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>-1</v>
+      </c>
+      <c r="AN22">
+        <v>-1</v>
+      </c>
+      <c r="AO22">
+        <v>-1</v>
+      </c>
+      <c r="AP22">
+        <v>-1</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2026-10-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Javor Ivanjica</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Borac Čačak</t>
+        </is>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>-1</v>
+      </c>
+      <c r="AN23">
+        <v>-1</v>
+      </c>
+      <c r="AO23">
+        <v>-1</v>
+      </c>
+      <c r="AP23">
+        <v>-1</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2026-10-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Semendrija 1924</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Voždovac</t>
+        </is>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>-1</v>
+      </c>
+      <c r="AN24">
+        <v>-1</v>
+      </c>
+      <c r="AO24">
+        <v>-1</v>
+      </c>
+      <c r="AP24">
+        <v>-1</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>2026-10-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Bačka Topola</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grafičar</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>-1</v>
+      </c>
+      <c r="AN25">
+        <v>-1</v>
+      </c>
+      <c r="AO25">
+        <v>-1</v>
+      </c>
+      <c r="AP25">
+        <v>-1</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>2026-10-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Teleoptik</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bor</t>
+        </is>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>-1</v>
+      </c>
+      <c r="AN26">
+        <v>-1</v>
+      </c>
+      <c r="AO26">
+        <v>-1</v>
+      </c>
+      <c r="AP26">
+        <v>-1</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>2026-10-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Jedinstvo Ub</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dubočica</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>-1</v>
+      </c>
+      <c r="AN27">
+        <v>-1</v>
+      </c>
+      <c r="AO27">
+        <v>-1</v>
+      </c>
+      <c r="AP27">
+        <v>-1</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>2026-10-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>OFK Vršac</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Metalac GM</t>
+        </is>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>-1</v>
+      </c>
+      <c r="AN28">
+        <v>-1</v>
+      </c>
+      <c r="AO28">
+        <v>-1</v>
+      </c>
+      <c r="AP28">
+        <v>-1</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>2026-10-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Napredak</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Loznica</t>
+        </is>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>-1</v>
+      </c>
+      <c r="AN29">
+        <v>-1</v>
+      </c>
+      <c r="AO29">
+        <v>-1</v>
+      </c>
+      <c r="AP29">
+        <v>-1</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>2026-10-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Serbia Prva Liga</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Spartak Subotica</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Naftagas</t>
+        </is>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>0</v>
+      </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>0</v>
+      </c>
+      <c r="AK30">
+        <v>0</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>-1</v>
+      </c>
+      <c r="AN30">
+        <v>-1</v>
+      </c>
+      <c r="AO30">
+        <v>-1</v>
+      </c>
+      <c r="AP30">
+        <v>-1</v>
+      </c>
+      <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>2026-10-02 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>21:35</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Fortaleza</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Náutico</t>
         </is>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
-      <c r="AA20">
-        <v>0</v>
-      </c>
-      <c r="AB20">
-        <v>0</v>
-      </c>
-      <c r="AC20">
-        <v>0</v>
-      </c>
-      <c r="AD20">
-        <v>0</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
-        <v>0</v>
-      </c>
-      <c r="AG20">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>0</v>
-      </c>
-      <c r="AK20">
-        <v>0</v>
-      </c>
-      <c r="AL20">
-        <v>0</v>
-      </c>
-      <c r="AM20">
-        <v>-1</v>
-      </c>
-      <c r="AN20">
-        <v>-1</v>
-      </c>
-      <c r="AO20">
-        <v>-1</v>
-      </c>
-      <c r="AP20">
-        <v>-1</v>
-      </c>
-      <c r="AQ20">
-        <v>0</v>
-      </c>
-      <c r="AR20">
-        <v>0</v>
-      </c>
-      <c r="AS20">
-        <v>0</v>
-      </c>
-      <c r="AT20">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>0</v>
+      </c>
+      <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>-1</v>
+      </c>
+      <c r="AN31">
+        <v>-1</v>
+      </c>
+      <c r="AO31">
+        <v>-1</v>
+      </c>
+      <c r="AP31">
+        <v>-1</v>
+      </c>
+      <c r="AQ31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
         <is>
           <t>2026-10-02 21:35:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Seattle Reign</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>North Carolina Courage</t>
+        </is>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>-1</v>
+      </c>
+      <c r="AN32">
+        <v>-1</v>
+      </c>
+      <c r="AO32">
+        <v>-1</v>
+      </c>
+      <c r="AP32">
+        <v>-1</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>2026-10-02 23:00:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G9">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G11">

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G26">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G30">

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G11">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G30">

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G30">

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G30">

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G30">

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G30">

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -970,40 +970,40 @@
         <v>2.87</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC4">
         <v>1.8</v>
@@ -1012,13 +1012,13 @@
         <v>2</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="O8">
-        <v>4.05</v>
+        <v>3.44</v>
       </c>
       <c r="P8">
-        <v>4.42</v>
+        <v>3.34</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.86</v>
+        <v>3.51</v>
       </c>
       <c r="O10">
-        <v>3.54</v>
+        <v>3.84</v>
       </c>
       <c r="P10">
-        <v>2.11</v>
+        <v>1.87</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>4.5</v>
+        <v>2.86</v>
       </c>
       <c r="O11">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="P11">
-        <v>1.62</v>
+        <v>2.11</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G28">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G30">

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -1459,55 +1459,55 @@
         <v>2.15</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.05</v>
+        <v>4.5</v>
       </c>
       <c r="O8">
-        <v>3.44</v>
+        <v>3.75</v>
       </c>
       <c r="P8">
-        <v>3.34</v>
+        <v>1.62</v>
       </c>
       <c r="Q8">
-        <v>2.35</v>
+        <v>3.3</v>
       </c>
       <c r="R8">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="U8">
-        <v>2.38</v>
+        <v>2.69</v>
       </c>
       <c r="V8">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="AA8">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AB8">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AC8">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AD8">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE8">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF8">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AG8">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK8">
-        <v>1.88</v>
+        <v>1.4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,31 +1776,31 @@
         </is>
       </c>
       <c r="N9">
-        <v>4.5</v>
+        <v>3.51</v>
       </c>
       <c r="O9">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="P9">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="Q9">
-        <v>3.3</v>
+        <v>4.01</v>
       </c>
       <c r="R9">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="S9">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T9">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="U9">
-        <v>2.69</v>
+        <v>2.24</v>
       </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="W9">
         <v>1.11</v>
@@ -1809,47 +1809,47 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
+        <v>1.14</v>
+      </c>
+      <c r="Z9">
+        <v>4.45</v>
+      </c>
+      <c r="AA9">
+        <v>1.53</v>
+      </c>
+      <c r="AB9">
+        <v>2.29</v>
+      </c>
+      <c r="AC9">
+        <v>2.3</v>
+      </c>
+      <c r="AD9">
+        <v>1.49</v>
+      </c>
+      <c r="AE9">
+        <v>1.18</v>
+      </c>
+      <c r="AF9">
+        <v>1.5</v>
+      </c>
+      <c r="AG9">
+        <v>2.38</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>1.17</v>
+      </c>
+      <c r="AK9">
         <v>1.22</v>
-      </c>
-      <c r="Z9">
-        <v>3.5</v>
-      </c>
-      <c r="AA9">
-        <v>1.83</v>
-      </c>
-      <c r="AB9">
-        <v>1.97</v>
-      </c>
-      <c r="AC9">
-        <v>2.88</v>
-      </c>
-      <c r="AD9">
-        <v>1.32</v>
-      </c>
-      <c r="AE9">
-        <v>1.14</v>
-      </c>
-      <c r="AF9">
-        <v>1.61</v>
-      </c>
-      <c r="AG9">
-        <v>2.16</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.33</v>
-      </c>
-      <c r="AK9">
-        <v>1.4</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,31 +1939,31 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.51</v>
+        <v>2.86</v>
       </c>
       <c r="O10">
-        <v>3.84</v>
+        <v>3.54</v>
       </c>
       <c r="P10">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="Q10">
-        <v>4.01</v>
+        <v>3.24</v>
       </c>
       <c r="R10">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="S10">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T10">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="U10">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="V10">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W10">
         <v>1.11</v>
@@ -1972,32 +1972,32 @@
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="Z10">
-        <v>4.45</v>
+        <v>4.41</v>
       </c>
       <c r="AA10">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AB10">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="AC10">
+        <v>2.52</v>
+      </c>
+      <c r="AD10">
+        <v>1.48</v>
+      </c>
+      <c r="AE10">
+        <v>1.13</v>
+      </c>
+      <c r="AF10">
+        <v>1.55</v>
+      </c>
+      <c r="AG10">
         <v>2.3</v>
       </c>
-      <c r="AD10">
-        <v>1.49</v>
-      </c>
-      <c r="AE10">
-        <v>1.18</v>
-      </c>
-      <c r="AF10">
-        <v>1.5</v>
-      </c>
-      <c r="AG10">
-        <v>2.38</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.86</v>
+        <v>2.05</v>
       </c>
       <c r="O11">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="P11">
-        <v>2.11</v>
+        <v>3.34</v>
       </c>
       <c r="Q11">
+        <v>2.35</v>
+      </c>
+      <c r="R11">
+        <v>2.14</v>
+      </c>
+      <c r="S11">
+        <v>1.3</v>
+      </c>
+      <c r="T11">
         <v>3.24</v>
-      </c>
-      <c r="R11">
-        <v>2.36</v>
-      </c>
-      <c r="S11">
-        <v>1.29</v>
-      </c>
-      <c r="T11">
-        <v>3.25</v>
       </c>
       <c r="U11">
         <v>2.38</v>
       </c>
       <c r="V11">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
         <v>1.19</v>
       </c>
       <c r="Z11">
-        <v>4.41</v>
+        <v>3.78</v>
       </c>
       <c r="AA11">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AB11">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AC11">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="AD11">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="AE11">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK11">
-        <v>1.3</v>
+        <v>1.88</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC15">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q32">
         <v>0</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.86</v>
+        <v>2.05</v>
       </c>
       <c r="O10">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="P10">
-        <v>2.11</v>
+        <v>3.34</v>
       </c>
       <c r="Q10">
+        <v>2.35</v>
+      </c>
+      <c r="R10">
+        <v>2.14</v>
+      </c>
+      <c r="S10">
+        <v>1.3</v>
+      </c>
+      <c r="T10">
         <v>3.24</v>
-      </c>
-      <c r="R10">
-        <v>2.36</v>
-      </c>
-      <c r="S10">
-        <v>1.29</v>
-      </c>
-      <c r="T10">
-        <v>3.25</v>
       </c>
       <c r="U10">
         <v>2.38</v>
       </c>
       <c r="V10">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
         <v>1.19</v>
       </c>
       <c r="Z10">
-        <v>4.41</v>
+        <v>3.78</v>
       </c>
       <c r="AA10">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AB10">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AC10">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="AD10">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="AE10">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF10">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AG10">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK10">
-        <v>1.3</v>
+        <v>1.88</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.05</v>
+        <v>2.86</v>
       </c>
       <c r="O11">
-        <v>3.44</v>
+        <v>3.54</v>
       </c>
       <c r="P11">
-        <v>3.34</v>
+        <v>2.11</v>
       </c>
       <c r="Q11">
-        <v>2.35</v>
+        <v>3.24</v>
       </c>
       <c r="R11">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T11">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="U11">
         <v>2.38</v>
       </c>
       <c r="V11">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W11">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
         <v>1.19</v>
       </c>
       <c r="Z11">
-        <v>3.78</v>
+        <v>4.41</v>
       </c>
       <c r="AA11">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="AB11">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AC11">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="AD11">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="AE11">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF11">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AG11">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>1.88</v>
+        <v>1.3</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -3565,17 +3565,17 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3728,17 +3728,17 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q21">
         <v>0</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -1296,55 +1296,55 @@
         <v>2.51</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.86</v>
+        <v>1.58</v>
       </c>
       <c r="O11">
-        <v>3.54</v>
+        <v>4.05</v>
       </c>
       <c r="P11">
-        <v>2.11</v>
+        <v>4.42</v>
       </c>
       <c r="Q11">
-        <v>3.24</v>
+        <v>2.1</v>
       </c>
       <c r="R11">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="S11">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T11">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="U11">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="V11">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="Z11">
-        <v>4.41</v>
+        <v>4.8</v>
       </c>
       <c r="AA11">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AB11">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AC11">
-        <v>2.52</v>
+        <v>2.24</v>
       </c>
       <c r="AD11">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AE11">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF11">
         <v>1.55</v>
       </c>
       <c r="AG11">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK11">
-        <v>1.3</v>
+        <v>2.08</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.58</v>
+        <v>2.86</v>
       </c>
       <c r="O12">
-        <v>4.05</v>
+        <v>3.54</v>
       </c>
       <c r="P12">
-        <v>4.42</v>
+        <v>2.11</v>
       </c>
       <c r="Q12">
-        <v>2.1</v>
+        <v>3.24</v>
       </c>
       <c r="R12">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="S12">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T12">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="U12">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V12">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="W12">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="Z12">
-        <v>4.8</v>
+        <v>4.41</v>
       </c>
       <c r="AA12">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AB12">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AC12">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="AD12">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AE12">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF12">
         <v>1.55</v>
       </c>
       <c r="AG12">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>2.08</v>
+        <v>1.3</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2763,34 +2763,34 @@
         <v>2.81</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA15">
         <v>1.85</v>
@@ -2799,19 +2799,19 @@
         <v>1.83</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3252,34 +3252,34 @@
         <v>2.51</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA18">
         <v>2.2</v>
@@ -3288,19 +3288,19 @@
         <v>1.57</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G30">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL31">
         <v>0</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -3904,55 +3904,55 @@
         <v>1.7</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -5534,55 +5534,55 @@
         <v>2.54</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL32">
         <v>0</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="O10">
-        <v>3.44</v>
+        <v>4.05</v>
       </c>
       <c r="P10">
-        <v>3.34</v>
+        <v>4.42</v>
       </c>
       <c r="Q10">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="R10">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T10">
-        <v>3.24</v>
+        <v>3.75</v>
       </c>
       <c r="U10">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="W10">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="Z10">
-        <v>3.78</v>
+        <v>4.8</v>
       </c>
       <c r="AA10">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AB10">
-        <v>2.05</v>
+        <v>2.42</v>
       </c>
       <c r="AC10">
-        <v>2.78</v>
+        <v>2.24</v>
       </c>
       <c r="AD10">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="AE10">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AF10">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AG10">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK10">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.58</v>
+        <v>2.86</v>
       </c>
       <c r="O11">
-        <v>4.05</v>
+        <v>3.54</v>
       </c>
       <c r="P11">
-        <v>4.42</v>
+        <v>2.11</v>
       </c>
       <c r="Q11">
-        <v>2.1</v>
+        <v>3.24</v>
       </c>
       <c r="R11">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="S11">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T11">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="U11">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V11">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="W11">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="Z11">
-        <v>4.8</v>
+        <v>4.41</v>
       </c>
       <c r="AA11">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AB11">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AC11">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="AD11">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AE11">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF11">
         <v>1.55</v>
       </c>
       <c r="AG11">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>2.08</v>
+        <v>1.3</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.86</v>
+        <v>2.05</v>
       </c>
       <c r="O12">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="P12">
-        <v>2.11</v>
+        <v>3.34</v>
       </c>
       <c r="Q12">
+        <v>2.35</v>
+      </c>
+      <c r="R12">
+        <v>2.14</v>
+      </c>
+      <c r="S12">
+        <v>1.3</v>
+      </c>
+      <c r="T12">
         <v>3.24</v>
-      </c>
-      <c r="R12">
-        <v>2.36</v>
-      </c>
-      <c r="S12">
-        <v>1.29</v>
-      </c>
-      <c r="T12">
-        <v>3.25</v>
       </c>
       <c r="U12">
         <v>2.38</v>
       </c>
       <c r="V12">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
         <v>1.19</v>
       </c>
       <c r="Z12">
-        <v>4.41</v>
+        <v>3.78</v>
       </c>
       <c r="AA12">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AB12">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AC12">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="AD12">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="AE12">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF12">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AG12">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK12">
-        <v>1.3</v>
+        <v>1.88</v>
       </c>
       <c r="AL12">
         <v>0</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.86</v>
+        <v>2.05</v>
       </c>
       <c r="O11">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="P11">
-        <v>2.11</v>
+        <v>3.34</v>
       </c>
       <c r="Q11">
+        <v>2.35</v>
+      </c>
+      <c r="R11">
+        <v>2.14</v>
+      </c>
+      <c r="S11">
+        <v>1.3</v>
+      </c>
+      <c r="T11">
         <v>3.24</v>
-      </c>
-      <c r="R11">
-        <v>2.36</v>
-      </c>
-      <c r="S11">
-        <v>1.29</v>
-      </c>
-      <c r="T11">
-        <v>3.25</v>
       </c>
       <c r="U11">
         <v>2.38</v>
       </c>
       <c r="V11">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
         <v>1.19</v>
       </c>
       <c r="Z11">
-        <v>4.41</v>
+        <v>3.78</v>
       </c>
       <c r="AA11">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AB11">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AC11">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="AD11">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="AE11">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK11">
-        <v>1.3</v>
+        <v>1.88</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.05</v>
+        <v>2.86</v>
       </c>
       <c r="O12">
-        <v>3.44</v>
+        <v>3.54</v>
       </c>
       <c r="P12">
-        <v>3.34</v>
+        <v>2.11</v>
       </c>
       <c r="Q12">
-        <v>2.35</v>
+        <v>3.24</v>
       </c>
       <c r="R12">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="S12">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T12">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="U12">
         <v>2.38</v>
       </c>
       <c r="V12">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W12">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
         <v>1.19</v>
       </c>
       <c r="Z12">
-        <v>3.78</v>
+        <v>4.41</v>
       </c>
       <c r="AA12">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="AB12">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AC12">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="AD12">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="AE12">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF12">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AG12">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>1.88</v>
+        <v>1.3</v>
       </c>
       <c r="AL12">
         <v>0</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.05</v>
+        <v>2.86</v>
       </c>
       <c r="O11">
-        <v>3.44</v>
+        <v>3.54</v>
       </c>
       <c r="P11">
-        <v>3.34</v>
+        <v>2.11</v>
       </c>
       <c r="Q11">
-        <v>2.35</v>
+        <v>3.24</v>
       </c>
       <c r="R11">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T11">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="U11">
         <v>2.38</v>
       </c>
       <c r="V11">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W11">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
         <v>1.19</v>
       </c>
       <c r="Z11">
-        <v>3.78</v>
+        <v>4.41</v>
       </c>
       <c r="AA11">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="AB11">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AC11">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="AD11">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="AE11">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF11">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AG11">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>1.88</v>
+        <v>1.3</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.86</v>
+        <v>2.05</v>
       </c>
       <c r="O12">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="P12">
-        <v>2.11</v>
+        <v>3.34</v>
       </c>
       <c r="Q12">
+        <v>2.35</v>
+      </c>
+      <c r="R12">
+        <v>2.14</v>
+      </c>
+      <c r="S12">
+        <v>1.3</v>
+      </c>
+      <c r="T12">
         <v>3.24</v>
-      </c>
-      <c r="R12">
-        <v>2.36</v>
-      </c>
-      <c r="S12">
-        <v>1.29</v>
-      </c>
-      <c r="T12">
-        <v>3.25</v>
       </c>
       <c r="U12">
         <v>2.38</v>
       </c>
       <c r="V12">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
         <v>1.19</v>
       </c>
       <c r="Z12">
-        <v>4.41</v>
+        <v>3.78</v>
       </c>
       <c r="AA12">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AB12">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AC12">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="AD12">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="AE12">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF12">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AG12">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK12">
-        <v>1.3</v>
+        <v>1.88</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3415,55 +3415,55 @@
         <v>4.8</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -961,31 +961,31 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="O4">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P4">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="Q4">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R4">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="S4">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="T4">
         <v>4.75</v>
       </c>
       <c r="U4">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V4">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="W4">
         <v>1.22</v>
@@ -994,25 +994,25 @@
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Z4">
-        <v>6.95</v>
+        <v>8</v>
       </c>
       <c r="AA4">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AB4">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AC4">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AD4">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AE4">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AF4">
         <v>1.3</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AK4">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1287,16 +1287,16 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.01</v>
+        <v>2.45</v>
       </c>
       <c r="O6">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="P6">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="Q6">
-        <v>3.24</v>
+        <v>3.34</v>
       </c>
       <c r="R6">
         <v>1.98</v>
@@ -1338,13 +1338,13 @@
         <v>1.24</v>
       </c>
       <c r="AE6">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG6">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.4</v>
       </c>
       <c r="AK6">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.06</v>
+        <v>3.25</v>
       </c>
       <c r="O7">
+        <v>3.5</v>
+      </c>
+      <c r="P7">
+        <v>2</v>
+      </c>
+      <c r="Q7">
         <v>3.6</v>
-      </c>
-      <c r="P7">
-        <v>2.15</v>
-      </c>
-      <c r="Q7">
-        <v>3.8</v>
       </c>
       <c r="R7">
         <v>2.48</v>
@@ -1471,13 +1471,13 @@
         <v>3.46</v>
       </c>
       <c r="U7">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="V7">
         <v>1.57</v>
       </c>
       <c r="W7">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
         <v>1.01</v>
@@ -1489,10 +1489,10 @@
         <v>4.88</v>
       </c>
       <c r="AA7">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB7">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AC7">
         <v>2.42</v>
@@ -1507,7 +1507,7 @@
         <v>1.48</v>
       </c>
       <c r="AG7">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK7">
         <v>1.3</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="O8">
+        <v>3.64</v>
+      </c>
+      <c r="P8">
+        <v>1.84</v>
+      </c>
+      <c r="Q8">
+        <v>4.01</v>
+      </c>
+      <c r="R8">
+        <v>2.48</v>
+      </c>
+      <c r="S8">
+        <v>1.22</v>
+      </c>
+      <c r="T8">
         <v>3.75</v>
       </c>
-      <c r="P8">
-        <v>1.62</v>
-      </c>
-      <c r="Q8">
-        <v>3.3</v>
-      </c>
-      <c r="R8">
-        <v>2.2</v>
-      </c>
-      <c r="S8">
-        <v>1.33</v>
-      </c>
-      <c r="T8">
-        <v>3</v>
-      </c>
       <c r="U8">
-        <v>2.69</v>
+        <v>2.24</v>
       </c>
       <c r="V8">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
+        <v>1.16</v>
+      </c>
+      <c r="Z8">
+        <v>4.45</v>
+      </c>
+      <c r="AA8">
+        <v>1.53</v>
+      </c>
+      <c r="AB8">
+        <v>2.29</v>
+      </c>
+      <c r="AC8">
+        <v>2.3</v>
+      </c>
+      <c r="AD8">
+        <v>1.49</v>
+      </c>
+      <c r="AE8">
+        <v>1.18</v>
+      </c>
+      <c r="AF8">
+        <v>1.5</v>
+      </c>
+      <c r="AG8">
+        <v>2.34</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <v>1.19</v>
+      </c>
+      <c r="AK8">
         <v>1.22</v>
-      </c>
-      <c r="Z8">
-        <v>3.5</v>
-      </c>
-      <c r="AA8">
-        <v>1.83</v>
-      </c>
-      <c r="AB8">
-        <v>1.97</v>
-      </c>
-      <c r="AC8">
-        <v>2.88</v>
-      </c>
-      <c r="AD8">
-        <v>1.32</v>
-      </c>
-      <c r="AE8">
-        <v>1.14</v>
-      </c>
-      <c r="AF8">
-        <v>1.61</v>
-      </c>
-      <c r="AG8">
-        <v>2.16</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.33</v>
-      </c>
-      <c r="AK8">
-        <v>1.4</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,65 +1776,65 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.51</v>
+        <v>1.59</v>
       </c>
       <c r="O9">
-        <v>3.84</v>
+        <v>3.94</v>
       </c>
       <c r="P9">
-        <v>1.87</v>
+        <v>4.48</v>
       </c>
       <c r="Q9">
-        <v>4.01</v>
+        <v>2.11</v>
       </c>
       <c r="R9">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="S9">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T9">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U9">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V9">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z9">
-        <v>4.45</v>
+        <v>4.9</v>
       </c>
       <c r="AA9">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB9">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AC9">
+        <v>2.22</v>
+      </c>
+      <c r="AD9">
+        <v>1.56</v>
+      </c>
+      <c r="AE9">
+        <v>1.19</v>
+      </c>
+      <c r="AF9">
+        <v>1.55</v>
+      </c>
+      <c r="AG9">
         <v>2.3</v>
       </c>
-      <c r="AD9">
-        <v>1.49</v>
-      </c>
-      <c r="AE9">
-        <v>1.18</v>
-      </c>
-      <c r="AF9">
-        <v>1.5</v>
-      </c>
-      <c r="AG9">
-        <v>2.38</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK9">
-        <v>1.22</v>
+        <v>2.2</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.58</v>
+        <v>2.8</v>
       </c>
       <c r="O10">
-        <v>4.05</v>
+        <v>3.72</v>
       </c>
       <c r="P10">
-        <v>4.42</v>
+        <v>2.16</v>
       </c>
       <c r="Q10">
-        <v>2.1</v>
+        <v>3.26</v>
       </c>
       <c r="R10">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="S10">
         <v>1.25</v>
       </c>
       <c r="T10">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="U10">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V10">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="W10">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z10">
-        <v>4.8</v>
+        <v>4.41</v>
       </c>
       <c r="AA10">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AB10">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AC10">
-        <v>2.24</v>
+        <v>2.49</v>
       </c>
       <c r="AD10">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AE10">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AG10">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>2.08</v>
+        <v>1.36</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.86</v>
+        <v>1.88</v>
       </c>
       <c r="O11">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="P11">
-        <v>2.11</v>
+        <v>3.75</v>
       </c>
       <c r="Q11">
+        <v>2.26</v>
+      </c>
+      <c r="R11">
+        <v>2.26</v>
+      </c>
+      <c r="S11">
+        <v>1.3</v>
+      </c>
+      <c r="T11">
         <v>3.24</v>
       </c>
-      <c r="R11">
-        <v>2.36</v>
-      </c>
-      <c r="S11">
-        <v>1.29</v>
-      </c>
-      <c r="T11">
-        <v>3.25</v>
-      </c>
       <c r="U11">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="V11">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
         <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
         <v>1.19</v>
       </c>
       <c r="Z11">
-        <v>4.41</v>
+        <v>3.8</v>
       </c>
       <c r="AA11">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="AB11">
-        <v>2.17</v>
+        <v>1.99</v>
       </c>
       <c r="AC11">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="AD11">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AE11">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AG11">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK11">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,34 +2265,34 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="O12">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>3.34</v>
+        <v>2.02</v>
       </c>
       <c r="Q12">
-        <v>2.35</v>
+        <v>3.95</v>
       </c>
       <c r="R12">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
         <v>1.3</v>
       </c>
       <c r="T12">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V12">
         <v>1.46</v>
       </c>
       <c r="W12">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
         <v>1.03</v>
@@ -2301,28 +2301,28 @@
         <v>1.19</v>
       </c>
       <c r="Z12">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="AA12">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB12">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AC12">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="AD12">
         <v>1.34</v>
       </c>
       <c r="AE12">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AG12">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>1.88</v>
+        <v>1.25</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N20">
@@ -3578,55 +3578,55 @@
         <v>4.11</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL20">
         <v>0</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,31 +2102,31 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.88</v>
+        <v>3.3</v>
       </c>
       <c r="O11">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P11">
-        <v>3.75</v>
+        <v>2.02</v>
       </c>
       <c r="Q11">
-        <v>2.26</v>
+        <v>3.95</v>
       </c>
       <c r="R11">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S11">
         <v>1.3</v>
       </c>
       <c r="T11">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="U11">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V11">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W11">
         <v>1.11</v>
@@ -2138,28 +2138,28 @@
         <v>1.19</v>
       </c>
       <c r="Z11">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="AA11">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB11">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="AC11">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="AD11">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE11">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AG11">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>1.95</v>
+        <v>1.25</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,31 +2265,31 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.3</v>
+        <v>1.88</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P12">
-        <v>2.02</v>
+        <v>3.75</v>
       </c>
       <c r="Q12">
-        <v>3.95</v>
+        <v>2.26</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="S12">
         <v>1.3</v>
       </c>
       <c r="T12">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="U12">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V12">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
         <v>1.11</v>
@@ -2301,29 +2301,29 @@
         <v>1.19</v>
       </c>
       <c r="Z12">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="AA12">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB12">
+        <v>1.99</v>
+      </c>
+      <c r="AC12">
+        <v>2.74</v>
+      </c>
+      <c r="AD12">
+        <v>1.35</v>
+      </c>
+      <c r="AE12">
+        <v>1.15</v>
+      </c>
+      <c r="AF12">
+        <v>1.66</v>
+      </c>
+      <c r="AG12">
         <v>2.04</v>
       </c>
-      <c r="AC12">
-        <v>2.86</v>
-      </c>
-      <c r="AD12">
-        <v>1.34</v>
-      </c>
-      <c r="AE12">
-        <v>1.1</v>
-      </c>
-      <c r="AF12">
-        <v>1.63</v>
-      </c>
-      <c r="AG12">
-        <v>2.1</v>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK12">
-        <v>1.25</v>
+        <v>1.95</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2754,34 +2754,34 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="O15">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="Q15">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="R15">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="S15">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T15">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U15">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="V15">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W15">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
         <v>1</v>
@@ -2793,10 +2793,10 @@
         <v>3.42</v>
       </c>
       <c r="AA15">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB15">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC15">
         <v>3.08</v>
@@ -2827,7 +2827,7 @@
         <v>1.27</v>
       </c>
       <c r="AK15">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU32"/>
+  <dimension ref="A1:AU24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -964,10 +964,10 @@
         <v>2.04</v>
       </c>
       <c r="O4">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P4">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q4">
         <v>2.26</v>
@@ -976,10 +976,10 @@
         <v>2.54</v>
       </c>
       <c r="S4">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T4">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="U4">
         <v>1.86</v>
@@ -1619,7 +1619,7 @@
         <v>3.64</v>
       </c>
       <c r="P8">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="Q8">
         <v>4.01</v>
@@ -1797,7 +1797,7 @@
         <v>3.5</v>
       </c>
       <c r="U9">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V9">
         <v>1.57</v>
@@ -1818,7 +1818,7 @@
         <v>1.47</v>
       </c>
       <c r="AB9">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="AC9">
         <v>2.22</v>
@@ -1827,7 +1827,7 @@
         <v>1.56</v>
       </c>
       <c r="AE9">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AF9">
         <v>1.55</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.8</v>
+        <v>1.85</v>
       </c>
       <c r="O10">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="P10">
-        <v>2.16</v>
+        <v>3.8</v>
       </c>
       <c r="Q10">
-        <v>3.26</v>
+        <v>2.25</v>
       </c>
       <c r="R10">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="S10">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>3.62</v>
+        <v>3.24</v>
       </c>
       <c r="U10">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="V10">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
+        <v>1.19</v>
+      </c>
+      <c r="Z10">
+        <v>3.8</v>
+      </c>
+      <c r="AA10">
+        <v>1.75</v>
+      </c>
+      <c r="AB10">
+        <v>1.99</v>
+      </c>
+      <c r="AC10">
+        <v>2.74</v>
+      </c>
+      <c r="AD10">
+        <v>1.35</v>
+      </c>
+      <c r="AE10">
         <v>1.15</v>
       </c>
-      <c r="Z10">
-        <v>4.41</v>
-      </c>
-      <c r="AA10">
-        <v>1.59</v>
-      </c>
-      <c r="AB10">
-        <v>2.17</v>
-      </c>
-      <c r="AC10">
-        <v>2.49</v>
-      </c>
-      <c r="AD10">
-        <v>1.42</v>
-      </c>
-      <c r="AE10">
-        <v>1.13</v>
-      </c>
       <c r="AF10">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AG10">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK10">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.3</v>
+        <v>2.67</v>
       </c>
       <c r="O11">
-        <v>3.5</v>
+        <v>3.72</v>
       </c>
       <c r="P11">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="Q11">
-        <v>3.95</v>
+        <v>3.26</v>
       </c>
       <c r="R11">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T11">
-        <v>3.2</v>
+        <v>3.62</v>
       </c>
       <c r="U11">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V11">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z11">
-        <v>3.74</v>
+        <v>4.41</v>
       </c>
       <c r="AA11">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AB11">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="AC11">
-        <v>2.86</v>
+        <v>2.49</v>
       </c>
       <c r="AD11">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AE11">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF11">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AG11">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,31 +2265,31 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.88</v>
+        <v>3.45</v>
       </c>
       <c r="O12">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P12">
-        <v>3.75</v>
+        <v>1.98</v>
       </c>
       <c r="Q12">
-        <v>2.26</v>
+        <v>3.95</v>
       </c>
       <c r="R12">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
         <v>1.3</v>
       </c>
       <c r="T12">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W12">
         <v>1.11</v>
@@ -2301,28 +2301,28 @@
         <v>1.19</v>
       </c>
       <c r="Z12">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="AA12">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB12">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="AC12">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="AD12">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE12">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AG12">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>1.95</v>
+        <v>1.25</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="O13">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P13">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q13">
         <v>6</v>
@@ -2446,25 +2446,25 @@
         <v>1.22</v>
       </c>
       <c r="T13">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="U13">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V13">
         <v>1.65</v>
       </c>
       <c r="W13">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X13">
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z13">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA13">
         <v>1.44</v>
@@ -2476,16 +2476,16 @@
         <v>2.07</v>
       </c>
       <c r="AD13">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE13">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AF13">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG13">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>2.7</v>
+        <v>1.17</v>
       </c>
       <c r="AK13">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3243,34 +3243,34 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="O18">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="P18">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="Q18">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="R18">
         <v>1.95</v>
       </c>
       <c r="S18">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T18">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="U18">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V18">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W18">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X18">
         <v>1.02</v>
@@ -3282,10 +3282,10 @@
         <v>2.7</v>
       </c>
       <c r="AA18">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AB18">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC18">
         <v>4.15</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AK18">
         <v>1.4</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="O19">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="P19">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="Q19">
+        <v>2.3</v>
+      </c>
+      <c r="R19">
+        <v>2.05</v>
+      </c>
+      <c r="S19">
+        <v>1.45</v>
+      </c>
+      <c r="T19">
+        <v>2.55</v>
+      </c>
+      <c r="U19">
+        <v>3.3</v>
+      </c>
+      <c r="V19">
+        <v>1.29</v>
+      </c>
+      <c r="W19">
+        <v>1.03</v>
+      </c>
+      <c r="X19">
+        <v>1.03</v>
+      </c>
+      <c r="Y19">
+        <v>1.4</v>
+      </c>
+      <c r="Z19">
+        <v>2.56</v>
+      </c>
+      <c r="AA19">
         <v>2.38</v>
       </c>
-      <c r="R19">
-        <v>1.98</v>
-      </c>
-      <c r="S19">
-        <v>1.46</v>
-      </c>
-      <c r="T19">
-        <v>2.47</v>
-      </c>
-      <c r="U19">
-        <v>3.32</v>
-      </c>
-      <c r="V19">
-        <v>1.27</v>
-      </c>
-      <c r="W19">
-        <v>1</v>
-      </c>
-      <c r="X19">
+      <c r="AB19">
+        <v>1.55</v>
+      </c>
+      <c r="AC19">
+        <v>4.5</v>
+      </c>
+      <c r="AD19">
+        <v>1.13</v>
+      </c>
+      <c r="AE19">
         <v>1.02</v>
       </c>
-      <c r="Y19">
-        <v>1.38</v>
-      </c>
-      <c r="Z19">
-        <v>2.62</v>
-      </c>
-      <c r="AA19">
-        <v>2.29</v>
-      </c>
-      <c r="AB19">
-        <v>1.57</v>
-      </c>
-      <c r="AC19">
-        <v>4.33</v>
-      </c>
-      <c r="AD19">
-        <v>1.14</v>
-      </c>
-      <c r="AE19">
-        <v>1</v>
-      </c>
       <c r="AF19">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AG19">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK19">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4011,27 +4011,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-10-02 21:00:00</t>
+          <t>2026-10-02 21:35:00</t>
         </is>
       </c>
     </row>
@@ -4174,27 +4174,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4324,1310 +4324,6 @@
         <v>0</v>
       </c>
       <c r="AU24" t="inlineStr">
-        <is>
-          <t>2026-10-02 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Jedinstvo Ub</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Dubočica</t>
-        </is>
-      </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
-        <v>0</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>0</v>
-      </c>
-      <c r="V25">
-        <v>0</v>
-      </c>
-      <c r="W25">
-        <v>0</v>
-      </c>
-      <c r="X25">
-        <v>0</v>
-      </c>
-      <c r="Y25">
-        <v>0</v>
-      </c>
-      <c r="Z25">
-        <v>0</v>
-      </c>
-      <c r="AA25">
-        <v>0</v>
-      </c>
-      <c r="AB25">
-        <v>0</v>
-      </c>
-      <c r="AC25">
-        <v>0</v>
-      </c>
-      <c r="AD25">
-        <v>0</v>
-      </c>
-      <c r="AE25">
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <v>0</v>
-      </c>
-      <c r="AG25">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>0</v>
-      </c>
-      <c r="AK25">
-        <v>0</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>-1</v>
-      </c>
-      <c r="AN25">
-        <v>-1</v>
-      </c>
-      <c r="AO25">
-        <v>-1</v>
-      </c>
-      <c r="AP25">
-        <v>-1</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>2026-10-02 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Teleoptik</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Bor</t>
-        </is>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>0</v>
-      </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="X26">
-        <v>0</v>
-      </c>
-      <c r="Y26">
-        <v>0</v>
-      </c>
-      <c r="Z26">
-        <v>0</v>
-      </c>
-      <c r="AA26">
-        <v>0</v>
-      </c>
-      <c r="AB26">
-        <v>0</v>
-      </c>
-      <c r="AC26">
-        <v>0</v>
-      </c>
-      <c r="AD26">
-        <v>0</v>
-      </c>
-      <c r="AE26">
-        <v>0</v>
-      </c>
-      <c r="AF26">
-        <v>0</v>
-      </c>
-      <c r="AG26">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>0</v>
-      </c>
-      <c r="AK26">
-        <v>0</v>
-      </c>
-      <c r="AL26">
-        <v>0</v>
-      </c>
-      <c r="AM26">
-        <v>-1</v>
-      </c>
-      <c r="AN26">
-        <v>-1</v>
-      </c>
-      <c r="AO26">
-        <v>-1</v>
-      </c>
-      <c r="AP26">
-        <v>-1</v>
-      </c>
-      <c r="AQ26">
-        <v>0</v>
-      </c>
-      <c r="AR26">
-        <v>0</v>
-      </c>
-      <c r="AS26">
-        <v>0</v>
-      </c>
-      <c r="AT26">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>2026-10-02 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Semendrija 1924</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Voždovac</t>
-        </is>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>0</v>
-      </c>
-      <c r="V27">
-        <v>0</v>
-      </c>
-      <c r="W27">
-        <v>0</v>
-      </c>
-      <c r="X27">
-        <v>0</v>
-      </c>
-      <c r="Y27">
-        <v>0</v>
-      </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
-      <c r="AA27">
-        <v>0</v>
-      </c>
-      <c r="AB27">
-        <v>0</v>
-      </c>
-      <c r="AC27">
-        <v>0</v>
-      </c>
-      <c r="AD27">
-        <v>0</v>
-      </c>
-      <c r="AE27">
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <v>0</v>
-      </c>
-      <c r="AG27">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>0</v>
-      </c>
-      <c r="AK27">
-        <v>0</v>
-      </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>-1</v>
-      </c>
-      <c r="AN27">
-        <v>-1</v>
-      </c>
-      <c r="AO27">
-        <v>-1</v>
-      </c>
-      <c r="AP27">
-        <v>-1</v>
-      </c>
-      <c r="AQ27">
-        <v>0</v>
-      </c>
-      <c r="AR27">
-        <v>0</v>
-      </c>
-      <c r="AS27">
-        <v>0</v>
-      </c>
-      <c r="AT27">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>2026-10-02 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>OFK Vršac</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Metalac GM</t>
-        </is>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="P28">
-        <v>0</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>0</v>
-      </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="Y28">
-        <v>0</v>
-      </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AA28">
-        <v>0</v>
-      </c>
-      <c r="AB28">
-        <v>0</v>
-      </c>
-      <c r="AC28">
-        <v>0</v>
-      </c>
-      <c r="AD28">
-        <v>0</v>
-      </c>
-      <c r="AE28">
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <v>0</v>
-      </c>
-      <c r="AG28">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>0</v>
-      </c>
-      <c r="AK28">
-        <v>0</v>
-      </c>
-      <c r="AL28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>-1</v>
-      </c>
-      <c r="AN28">
-        <v>-1</v>
-      </c>
-      <c r="AO28">
-        <v>-1</v>
-      </c>
-      <c r="AP28">
-        <v>-1</v>
-      </c>
-      <c r="AQ28">
-        <v>0</v>
-      </c>
-      <c r="AR28">
-        <v>0</v>
-      </c>
-      <c r="AS28">
-        <v>0</v>
-      </c>
-      <c r="AT28">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>2026-10-02 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Napredak</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Loznica</t>
-        </is>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29">
-        <v>0</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
-      <c r="U29">
-        <v>0</v>
-      </c>
-      <c r="V29">
-        <v>0</v>
-      </c>
-      <c r="W29">
-        <v>0</v>
-      </c>
-      <c r="X29">
-        <v>0</v>
-      </c>
-      <c r="Y29">
-        <v>0</v>
-      </c>
-      <c r="Z29">
-        <v>0</v>
-      </c>
-      <c r="AA29">
-        <v>0</v>
-      </c>
-      <c r="AB29">
-        <v>0</v>
-      </c>
-      <c r="AC29">
-        <v>0</v>
-      </c>
-      <c r="AD29">
-        <v>0</v>
-      </c>
-      <c r="AE29">
-        <v>0</v>
-      </c>
-      <c r="AF29">
-        <v>0</v>
-      </c>
-      <c r="AG29">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>0</v>
-      </c>
-      <c r="AK29">
-        <v>0</v>
-      </c>
-      <c r="AL29">
-        <v>0</v>
-      </c>
-      <c r="AM29">
-        <v>-1</v>
-      </c>
-      <c r="AN29">
-        <v>-1</v>
-      </c>
-      <c r="AO29">
-        <v>-1</v>
-      </c>
-      <c r="AP29">
-        <v>-1</v>
-      </c>
-      <c r="AQ29">
-        <v>0</v>
-      </c>
-      <c r="AR29">
-        <v>0</v>
-      </c>
-      <c r="AS29">
-        <v>0</v>
-      </c>
-      <c r="AT29">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>2026-10-02 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Spartak Subotica</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Naftagas</t>
-        </is>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
-        <v>0</v>
-      </c>
-      <c r="P30">
-        <v>0</v>
-      </c>
-      <c r="Q30">
-        <v>0</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
-      <c r="U30">
-        <v>0</v>
-      </c>
-      <c r="V30">
-        <v>0</v>
-      </c>
-      <c r="W30">
-        <v>0</v>
-      </c>
-      <c r="X30">
-        <v>0</v>
-      </c>
-      <c r="Y30">
-        <v>0</v>
-      </c>
-      <c r="Z30">
-        <v>0</v>
-      </c>
-      <c r="AA30">
-        <v>0</v>
-      </c>
-      <c r="AB30">
-        <v>0</v>
-      </c>
-      <c r="AC30">
-        <v>0</v>
-      </c>
-      <c r="AD30">
-        <v>0</v>
-      </c>
-      <c r="AE30">
-        <v>0</v>
-      </c>
-      <c r="AF30">
-        <v>0</v>
-      </c>
-      <c r="AG30">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>0</v>
-      </c>
-      <c r="AK30">
-        <v>0</v>
-      </c>
-      <c r="AL30">
-        <v>0</v>
-      </c>
-      <c r="AM30">
-        <v>-1</v>
-      </c>
-      <c r="AN30">
-        <v>-1</v>
-      </c>
-      <c r="AO30">
-        <v>-1</v>
-      </c>
-      <c r="AP30">
-        <v>-1</v>
-      </c>
-      <c r="AQ30">
-        <v>0</v>
-      </c>
-      <c r="AR30">
-        <v>0</v>
-      </c>
-      <c r="AS30">
-        <v>0</v>
-      </c>
-      <c r="AT30">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>2026-10-02 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>21:35</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Fortaleza</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Náutico</t>
-        </is>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N31">
-        <v>1.82</v>
-      </c>
-      <c r="O31">
-        <v>3.5</v>
-      </c>
-      <c r="P31">
-        <v>4.6</v>
-      </c>
-      <c r="Q31">
-        <v>2.4</v>
-      </c>
-      <c r="R31">
-        <v>2.05</v>
-      </c>
-      <c r="S31">
-        <v>1.38</v>
-      </c>
-      <c r="T31">
-        <v>2.75</v>
-      </c>
-      <c r="U31">
-        <v>2.92</v>
-      </c>
-      <c r="V31">
-        <v>1.34</v>
-      </c>
-      <c r="W31">
-        <v>1.04</v>
-      </c>
-      <c r="X31">
-        <v>1.01</v>
-      </c>
-      <c r="Y31">
-        <v>1.31</v>
-      </c>
-      <c r="Z31">
-        <v>2.92</v>
-      </c>
-      <c r="AA31">
-        <v>2.09</v>
-      </c>
-      <c r="AB31">
-        <v>1.68</v>
-      </c>
-      <c r="AC31">
-        <v>3.74</v>
-      </c>
-      <c r="AD31">
-        <v>1.19</v>
-      </c>
-      <c r="AE31">
-        <v>1.02</v>
-      </c>
-      <c r="AF31">
-        <v>1.93</v>
-      </c>
-      <c r="AG31">
-        <v>1.78</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.26</v>
-      </c>
-      <c r="AK31">
-        <v>1.94</v>
-      </c>
-      <c r="AL31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>-1</v>
-      </c>
-      <c r="AN31">
-        <v>-1</v>
-      </c>
-      <c r="AO31">
-        <v>-1</v>
-      </c>
-      <c r="AP31">
-        <v>-1</v>
-      </c>
-      <c r="AQ31">
-        <v>0</v>
-      </c>
-      <c r="AR31">
-        <v>0</v>
-      </c>
-      <c r="AS31">
-        <v>0</v>
-      </c>
-      <c r="AT31">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>2026-10-02 21:35:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Seattle Reign</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>North Carolina Courage</t>
-        </is>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N32">
-        <v>2.44</v>
-      </c>
-      <c r="O32">
-        <v>3.26</v>
-      </c>
-      <c r="P32">
-        <v>2.54</v>
-      </c>
-      <c r="Q32">
-        <v>3.1</v>
-      </c>
-      <c r="R32">
-        <v>2.3</v>
-      </c>
-      <c r="S32">
-        <v>1.25</v>
-      </c>
-      <c r="T32">
-        <v>3.4</v>
-      </c>
-      <c r="U32">
-        <v>2.37</v>
-      </c>
-      <c r="V32">
-        <v>1.55</v>
-      </c>
-      <c r="W32">
-        <v>1.12</v>
-      </c>
-      <c r="X32">
-        <v>1.03</v>
-      </c>
-      <c r="Y32">
-        <v>1.15</v>
-      </c>
-      <c r="Z32">
-        <v>4.2</v>
-      </c>
-      <c r="AA32">
-        <v>1.61</v>
-      </c>
-      <c r="AB32">
-        <v>2.25</v>
-      </c>
-      <c r="AC32">
-        <v>2.53</v>
-      </c>
-      <c r="AD32">
-        <v>1.47</v>
-      </c>
-      <c r="AE32">
-        <v>1.15</v>
-      </c>
-      <c r="AF32">
-        <v>1.5</v>
-      </c>
-      <c r="AG32">
-        <v>2.38</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.3</v>
-      </c>
-      <c r="AK32">
-        <v>1.4</v>
-      </c>
-      <c r="AL32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>-1</v>
-      </c>
-      <c r="AN32">
-        <v>-1</v>
-      </c>
-      <c r="AO32">
-        <v>-1</v>
-      </c>
-      <c r="AP32">
-        <v>-1</v>
-      </c>
-      <c r="AQ32">
-        <v>0</v>
-      </c>
-      <c r="AR32">
-        <v>0</v>
-      </c>
-      <c r="AS32">
-        <v>0</v>
-      </c>
-      <c r="AT32">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
         <is>
           <t>2026-10-02 23:00:00</t>
         </is>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -1459,7 +1459,7 @@
         <v>2</v>
       </c>
       <c r="Q7">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R7">
         <v>2.48</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.22</v>
+        <v>1.8</v>
       </c>
       <c r="AK7">
         <v>1.3</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="O15">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P15">
-        <v>2.8</v>
+        <v>4.33</v>
       </c>
       <c r="Q15">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="R15">
-        <v>2.24</v>
+        <v>1.91</v>
       </c>
       <c r="S15">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="T15">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="U15">
-        <v>2.58</v>
+        <v>3.82</v>
       </c>
       <c r="V15">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="Y15">
-        <v>1.23</v>
+        <v>1.59</v>
       </c>
       <c r="Z15">
-        <v>3.42</v>
+        <v>2.32</v>
       </c>
       <c r="AA15">
-        <v>1.91</v>
+        <v>2.87</v>
       </c>
       <c r="AB15">
-        <v>1.87</v>
+        <v>1.36</v>
       </c>
       <c r="AC15">
-        <v>3.08</v>
+        <v>5.45</v>
       </c>
       <c r="AD15">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AE15">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF15">
-        <v>1.68</v>
+        <v>2.32</v>
       </c>
       <c r="AG15">
-        <v>2.06</v>
+        <v>1.53</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AK15">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-10-02 19:30:00</t>
+          <t>2026-10-02 19:00:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="O16">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q16">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="R16">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="S16">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T16">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="U16">
-        <v>2.9</v>
+        <v>2.58</v>
       </c>
       <c r="V16">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="W16">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
+        <v>1</v>
+      </c>
+      <c r="Y16">
+        <v>1.23</v>
+      </c>
+      <c r="Z16">
+        <v>3.42</v>
+      </c>
+      <c r="AA16">
+        <v>1.91</v>
+      </c>
+      <c r="AB16">
+        <v>1.87</v>
+      </c>
+      <c r="AC16">
+        <v>3.08</v>
+      </c>
+      <c r="AD16">
+        <v>1.28</v>
+      </c>
+      <c r="AE16">
         <v>1.06</v>
       </c>
-      <c r="Y16">
-        <v>1.33</v>
-      </c>
-      <c r="Z16">
-        <v>2.8</v>
-      </c>
-      <c r="AA16">
-        <v>2.18</v>
-      </c>
-      <c r="AB16">
+      <c r="AF16">
         <v>1.68</v>
       </c>
-      <c r="AC16">
-        <v>3.62</v>
-      </c>
-      <c r="AD16">
-        <v>1.21</v>
-      </c>
-      <c r="AE16">
-        <v>1.07</v>
-      </c>
-      <c r="AF16">
-        <v>1.85</v>
-      </c>
       <c r="AG16">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK16">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-10-02 20:00:00</t>
+          <t>2026-10-02 19:30:00</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O17">
         <v>3.4</v>
       </c>
       <c r="P17">
-        <v>3.26</v>
+        <v>3.6</v>
       </c>
       <c r="Q17">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="R17">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S17">
+        <v>1.41</v>
+      </c>
+      <c r="T17">
+        <v>2.88</v>
+      </c>
+      <c r="U17">
+        <v>2.8</v>
+      </c>
+      <c r="V17">
         <v>1.32</v>
       </c>
-      <c r="T17">
-        <v>3.1</v>
-      </c>
-      <c r="U17">
-        <v>2.45</v>
-      </c>
-      <c r="V17">
-        <v>1.44</v>
-      </c>
       <c r="W17">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z17">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="AA17">
+        <v>2.07</v>
+      </c>
+      <c r="AB17">
+        <v>1.78</v>
+      </c>
+      <c r="AC17">
+        <v>3.42</v>
+      </c>
+      <c r="AD17">
+        <v>1.23</v>
+      </c>
+      <c r="AE17">
+        <v>1.04</v>
+      </c>
+      <c r="AF17">
+        <v>1.81</v>
+      </c>
+      <c r="AG17">
+        <v>1.87</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>1.3</v>
+      </c>
+      <c r="AK17">
         <v>1.75</v>
-      </c>
-      <c r="AB17">
-        <v>1.97</v>
-      </c>
-      <c r="AC17">
-        <v>2.75</v>
-      </c>
-      <c r="AD17">
-        <v>1.4</v>
-      </c>
-      <c r="AE17">
-        <v>1.15</v>
-      </c>
-      <c r="AF17">
-        <v>1.68</v>
-      </c>
-      <c r="AG17">
-        <v>2.13</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.29</v>
-      </c>
-      <c r="AK17">
-        <v>1.7</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Univ. Concepción</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
+        <v>2.05</v>
+      </c>
+      <c r="O18">
+        <v>3.25</v>
+      </c>
+      <c r="P18">
+        <v>3.3</v>
+      </c>
+      <c r="Q18">
         <v>2.62</v>
       </c>
-      <c r="O18">
-        <v>3</v>
-      </c>
-      <c r="P18">
-        <v>2.5</v>
-      </c>
-      <c r="Q18">
-        <v>3.4</v>
-      </c>
       <c r="R18">
+        <v>2.2</v>
+      </c>
+      <c r="S18">
+        <v>1.32</v>
+      </c>
+      <c r="T18">
+        <v>3.1</v>
+      </c>
+      <c r="U18">
+        <v>2.45</v>
+      </c>
+      <c r="V18">
+        <v>1.48</v>
+      </c>
+      <c r="W18">
+        <v>1.1</v>
+      </c>
+      <c r="X18">
+        <v>1.04</v>
+      </c>
+      <c r="Y18">
+        <v>1.22</v>
+      </c>
+      <c r="Z18">
+        <v>3.75</v>
+      </c>
+      <c r="AA18">
+        <v>1.88</v>
+      </c>
+      <c r="AB18">
         <v>1.95</v>
       </c>
-      <c r="S18">
-        <v>1.49</v>
-      </c>
-      <c r="T18">
-        <v>2.39</v>
-      </c>
-      <c r="U18">
-        <v>3.4</v>
-      </c>
-      <c r="V18">
-        <v>1.29</v>
-      </c>
-      <c r="W18">
-        <v>1.03</v>
-      </c>
-      <c r="X18">
-        <v>1.02</v>
-      </c>
-      <c r="Y18">
+      <c r="AC18">
+        <v>2.95</v>
+      </c>
+      <c r="AD18">
         <v>1.36</v>
       </c>
-      <c r="Z18">
-        <v>2.7</v>
-      </c>
-      <c r="AA18">
-        <v>2.19</v>
-      </c>
-      <c r="AB18">
-        <v>1.58</v>
-      </c>
-      <c r="AC18">
-        <v>4.15</v>
-      </c>
-      <c r="AD18">
-        <v>1.16</v>
-      </c>
       <c r="AE18">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AF18">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AG18">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-10-02 20:30:00</t>
+          <t>2026-10-02 20:00:00</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,28 +3406,28 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.73</v>
+        <v>2.62</v>
       </c>
       <c r="O19">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="P19">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q19">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="R19">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S19">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="T19">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="U19">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V19">
         <v>1.29</v>
@@ -3436,51 +3436,51 @@
         <v>1.03</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
+        <v>1.36</v>
+      </c>
+      <c r="Z19">
+        <v>2.7</v>
+      </c>
+      <c r="AA19">
+        <v>2.19</v>
+      </c>
+      <c r="AB19">
+        <v>1.58</v>
+      </c>
+      <c r="AC19">
+        <v>4.15</v>
+      </c>
+      <c r="AD19">
+        <v>1.16</v>
+      </c>
+      <c r="AE19">
+        <v>1.01</v>
+      </c>
+      <c r="AF19">
+        <v>1.9</v>
+      </c>
+      <c r="AG19">
+        <v>1.8</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>1.31</v>
+      </c>
+      <c r="AK19">
         <v>1.4</v>
       </c>
-      <c r="Z19">
-        <v>2.56</v>
-      </c>
-      <c r="AA19">
-        <v>2.38</v>
-      </c>
-      <c r="AB19">
-        <v>1.55</v>
-      </c>
-      <c r="AC19">
-        <v>4.5</v>
-      </c>
-      <c r="AD19">
-        <v>1.13</v>
-      </c>
-      <c r="AE19">
-        <v>1.02</v>
-      </c>
-      <c r="AF19">
-        <v>2.15</v>
-      </c>
-      <c r="AG19">
-        <v>1.65</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.28</v>
-      </c>
-      <c r="AK19">
-        <v>1.91</v>
-      </c>
       <c r="AL19">
         <v>0</v>
       </c>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-10-02 20:45:00</t>
+          <t>2026-10-02 20:30:00</t>
         </is>
       </c>
     </row>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,81 +3569,81 @@
         </is>
       </c>
       <c r="N20">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="O20">
-        <v>2.95</v>
+        <v>3.42</v>
       </c>
       <c r="P20">
-        <v>4.11</v>
+        <v>5.2</v>
       </c>
       <c r="Q20">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="R20">
+        <v>2.05</v>
+      </c>
+      <c r="S20">
+        <v>1.45</v>
+      </c>
+      <c r="T20">
+        <v>2.55</v>
+      </c>
+      <c r="U20">
+        <v>3.3</v>
+      </c>
+      <c r="V20">
+        <v>1.29</v>
+      </c>
+      <c r="W20">
+        <v>1.03</v>
+      </c>
+      <c r="X20">
+        <v>1.03</v>
+      </c>
+      <c r="Y20">
+        <v>1.4</v>
+      </c>
+      <c r="Z20">
+        <v>2.56</v>
+      </c>
+      <c r="AA20">
+        <v>2.38</v>
+      </c>
+      <c r="AB20">
+        <v>1.55</v>
+      </c>
+      <c r="AC20">
+        <v>4.5</v>
+      </c>
+      <c r="AD20">
+        <v>1.13</v>
+      </c>
+      <c r="AE20">
+        <v>1.02</v>
+      </c>
+      <c r="AF20">
+        <v>2.15</v>
+      </c>
+      <c r="AG20">
+        <v>1.65</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>1.28</v>
+      </c>
+      <c r="AK20">
         <v>1.91</v>
       </c>
-      <c r="S20">
-        <v>1.53</v>
-      </c>
-      <c r="T20">
-        <v>2.38</v>
-      </c>
-      <c r="U20">
-        <v>3.78</v>
-      </c>
-      <c r="V20">
-        <v>1.19</v>
-      </c>
-      <c r="W20">
-        <v>1.04</v>
-      </c>
-      <c r="X20">
-        <v>1.07</v>
-      </c>
-      <c r="Y20">
-        <v>1.56</v>
-      </c>
-      <c r="Z20">
-        <v>2.36</v>
-      </c>
-      <c r="AA20">
-        <v>2.62</v>
-      </c>
-      <c r="AB20">
-        <v>1.38</v>
-      </c>
-      <c r="AC20">
-        <v>5.3</v>
-      </c>
-      <c r="AD20">
-        <v>1.09</v>
-      </c>
-      <c r="AE20">
-        <v>1.03</v>
-      </c>
-      <c r="AF20">
-        <v>2.28</v>
-      </c>
-      <c r="AG20">
-        <v>1.55</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.15</v>
-      </c>
-      <c r="AK20">
-        <v>1.73</v>
-      </c>
       <c r="AL20">
         <v>0</v>
       </c>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-10-02 21:00:00</t>
+          <t>2026-10-02 20:45:00</t>
         </is>
       </c>
     </row>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="O21">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P21">
         <v>3.3</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,52 +3904,52 @@
         <v>1.7</v>
       </c>
       <c r="Q22">
-        <v>4.2</v>
+        <v>3.82</v>
       </c>
       <c r="R22">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S22">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T22">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U22">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="V22">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="W22">
+        <v>1.14</v>
+      </c>
+      <c r="X22">
+        <v>1.02</v>
+      </c>
+      <c r="Y22">
         <v>1.11</v>
       </c>
-      <c r="X22">
-        <v>1</v>
-      </c>
-      <c r="Y22">
-        <v>1.19</v>
-      </c>
       <c r="Z22">
-        <v>3.78</v>
+        <v>4.35</v>
       </c>
       <c r="AA22">
-        <v>1.72</v>
+        <v>1.45</v>
       </c>
       <c r="AB22">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="AC22">
-        <v>2.76</v>
+        <v>2.42</v>
       </c>
       <c r="AD22">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE22">
         <v>1.13</v>
       </c>
       <c r="AF22">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AG22">
         <v>2.1</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -967,13 +967,13 @@
         <v>4</v>
       </c>
       <c r="P4">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="Q4">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R4">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="S4">
         <v>1.17</v>
@@ -982,13 +982,13 @@
         <v>4.6</v>
       </c>
       <c r="U4">
+        <v>1.96</v>
+      </c>
+      <c r="V4">
         <v>1.86</v>
       </c>
-      <c r="V4">
-        <v>1.96</v>
-      </c>
       <c r="W4">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X4">
         <v>1.01</v>
@@ -1003,16 +1003,16 @@
         <v>1.29</v>
       </c>
       <c r="AB4">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AC4">
         <v>1.74</v>
       </c>
       <c r="AD4">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AE4">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AF4">
         <v>1.3</v>
@@ -1293,7 +1293,7 @@
         <v>3</v>
       </c>
       <c r="P6">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="Q6">
         <v>3.34</v>
@@ -1613,16 +1613,16 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O8">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q8">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="R8">
         <v>2.48</v>
@@ -1634,7 +1634,7 @@
         <v>3.75</v>
       </c>
       <c r="U8">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="V8">
         <v>1.57</v>
@@ -1649,28 +1649,28 @@
         <v>1.16</v>
       </c>
       <c r="Z8">
-        <v>4.45</v>
+        <v>4.68</v>
       </c>
       <c r="AA8">
         <v>1.53</v>
       </c>
       <c r="AB8">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AC8">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD8">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AE8">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF8">
         <v>1.5</v>
       </c>
       <c r="AG8">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.19</v>
       </c>
       <c r="AK8">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="O9">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="P9">
         <v>4.48</v>
       </c>
       <c r="Q9">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="R9">
         <v>2.5</v>
@@ -1794,37 +1794,37 @@
         <v>1.22</v>
       </c>
       <c r="T9">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="U9">
         <v>2.15</v>
       </c>
       <c r="V9">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W9">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z9">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="AA9">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AB9">
         <v>2.47</v>
       </c>
       <c r="AC9">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="AD9">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="AE9">
         <v>1.23</v>
@@ -1939,28 +1939,28 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="O10">
         <v>3.7</v>
       </c>
       <c r="P10">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Q10">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R10">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="S10">
         <v>1.3</v>
       </c>
       <c r="T10">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="U10">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="V10">
         <v>1.44</v>
@@ -1972,47 +1972,47 @@
         <v>1.03</v>
       </c>
       <c r="Y10">
+        <v>1.21</v>
+      </c>
+      <c r="Z10">
+        <v>3.92</v>
+      </c>
+      <c r="AA10">
+        <v>1.76</v>
+      </c>
+      <c r="AB10">
+        <v>1.98</v>
+      </c>
+      <c r="AC10">
+        <v>2.69</v>
+      </c>
+      <c r="AD10">
+        <v>1.44</v>
+      </c>
+      <c r="AE10">
+        <v>1.13</v>
+      </c>
+      <c r="AF10">
+        <v>1.65</v>
+      </c>
+      <c r="AG10">
+        <v>2.08</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
         <v>1.19</v>
       </c>
-      <c r="Z10">
-        <v>3.8</v>
-      </c>
-      <c r="AA10">
-        <v>1.75</v>
-      </c>
-      <c r="AB10">
-        <v>1.99</v>
-      </c>
-      <c r="AC10">
-        <v>2.74</v>
-      </c>
-      <c r="AD10">
-        <v>1.35</v>
-      </c>
-      <c r="AE10">
-        <v>1.15</v>
-      </c>
-      <c r="AF10">
-        <v>1.66</v>
-      </c>
-      <c r="AG10">
-        <v>2.04</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.18</v>
-      </c>
       <c r="AK10">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.67</v>
+        <v>2.78</v>
       </c>
       <c r="O11">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="P11">
         <v>2.16</v>
       </c>
       <c r="Q11">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="R11">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="S11">
         <v>1.25</v>
       </c>
       <c r="T11">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="U11">
         <v>2.38</v>
@@ -2135,7 +2135,7 @@
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z11">
         <v>4.41</v>
@@ -2274,10 +2274,10 @@
         <v>1.98</v>
       </c>
       <c r="Q12">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S12">
         <v>1.3</v>
@@ -2298,28 +2298,28 @@
         <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z12">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="AA12">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AB12">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AC12">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="AD12">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF12">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG12">
         <v>2.1</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2431,22 +2431,22 @@
         <v>5.75</v>
       </c>
       <c r="O13">
-        <v>4.6</v>
+        <v>4.85</v>
       </c>
       <c r="P13">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Q13">
-        <v>6</v>
+        <v>5.97</v>
       </c>
       <c r="R13">
         <v>2.62</v>
       </c>
       <c r="S13">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T13">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="U13">
         <v>2.1</v>
@@ -2467,19 +2467,19 @@
         <v>5.75</v>
       </c>
       <c r="AA13">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB13">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AC13">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AD13">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE13">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF13">
         <v>1.59</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="O15">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P15">
         <v>4.33</v>
       </c>
       <c r="Q15">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="R15">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S15">
         <v>1.53</v>
@@ -2775,10 +2775,10 @@
         <v>2.38</v>
       </c>
       <c r="U15">
-        <v>3.82</v>
+        <v>3.87</v>
       </c>
       <c r="V15">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W15">
         <v>1.04</v>
@@ -2796,22 +2796,22 @@
         <v>2.87</v>
       </c>
       <c r="AB15">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC15">
-        <v>5.45</v>
+        <v>5.62</v>
       </c>
       <c r="AD15">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AE15">
         <v>1.03</v>
       </c>
       <c r="AF15">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AG15">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AK15">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2938,10 +2938,10 @@
         <v>3</v>
       </c>
       <c r="U16">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V16">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W16">
         <v>1.06</v>
@@ -2950,25 +2950,25 @@
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z16">
         <v>3.42</v>
       </c>
       <c r="AA16">
+        <v>1.85</v>
+      </c>
+      <c r="AB16">
         <v>1.91</v>
-      </c>
-      <c r="AB16">
-        <v>1.87</v>
       </c>
       <c r="AC16">
         <v>3.08</v>
       </c>
       <c r="AD16">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE16">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
         <v>1.68</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK16">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3098,7 +3098,7 @@
         <v>1.41</v>
       </c>
       <c r="T17">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="U17">
         <v>2.8</v>
@@ -3137,7 +3137,7 @@
         <v>1.81</v>
       </c>
       <c r="AG17">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3406,19 +3406,19 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O19">
         <v>3</v>
       </c>
       <c r="P19">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q19">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R19">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="S19">
         <v>1.49</v>
@@ -3439,22 +3439,22 @@
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="Z19">
         <v>2.7</v>
       </c>
       <c r="AA19">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AB19">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AC19">
-        <v>4.15</v>
+        <v>4.28</v>
       </c>
       <c r="AD19">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AE19">
         <v>1.01</v>
@@ -3463,7 +3463,7 @@
         <v>1.9</v>
       </c>
       <c r="AG19">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3590,10 +3590,10 @@
         <v>2.55</v>
       </c>
       <c r="U20">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V20">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W20">
         <v>1.03</v>
@@ -3602,16 +3602,16 @@
         <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="Z20">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AA20">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AB20">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC20">
         <v>4.5</v>
@@ -3620,7 +3620,7 @@
         <v>1.13</v>
       </c>
       <c r="AE20">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AF20">
         <v>2.15</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK20">
         <v>1.91</v>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N21">
@@ -3741,10 +3741,10 @@
         <v>3.3</v>
       </c>
       <c r="Q21">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="R21">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="S21">
         <v>1.56</v>
@@ -3753,7 +3753,7 @@
         <v>2.22</v>
       </c>
       <c r="U21">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="V21">
         <v>1.25</v>
@@ -3777,13 +3777,13 @@
         <v>1.4</v>
       </c>
       <c r="AC21">
-        <v>4.85</v>
+        <v>4.98</v>
       </c>
       <c r="AD21">
         <v>1.11</v>
       </c>
       <c r="AE21">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF21">
         <v>2.1</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -1456,7 +1456,7 @@
         <v>3.5</v>
       </c>
       <c r="P7">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q7">
         <v>3.8</v>
@@ -1468,7 +1468,7 @@
         <v>1.25</v>
       </c>
       <c r="T7">
-        <v>3.46</v>
+        <v>3.6</v>
       </c>
       <c r="U7">
         <v>2.25</v>
@@ -1483,7 +1483,7 @@
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z7">
         <v>4.88</v>
@@ -3424,7 +3424,7 @@
         <v>1.49</v>
       </c>
       <c r="T19">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="U19">
         <v>3.4</v>
@@ -3614,10 +3614,10 @@
         <v>1.57</v>
       </c>
       <c r="AC20">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AD20">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE20">
         <v>1</v>
@@ -3904,13 +3904,13 @@
         <v>1.7</v>
       </c>
       <c r="Q22">
-        <v>3.82</v>
+        <v>3.62</v>
       </c>
       <c r="R22">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T22">
         <v>3.6</v>
@@ -3928,19 +3928,19 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z22">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="AA22">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AB22">
-        <v>1.96</v>
+        <v>2.32</v>
       </c>
       <c r="AC22">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AD22">
         <v>1.47</v>
@@ -3952,7 +3952,7 @@
         <v>1.4</v>
       </c>
       <c r="AG22">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
+        <v>1.22</v>
+      </c>
+      <c r="AK22">
         <v>1.25</v>
-      </c>
-      <c r="AK22">
-        <v>1.22</v>
       </c>
       <c r="AL22">
         <v>0</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -2923,7 +2923,7 @@
         <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q16">
         <v>2.88</v>
@@ -2956,7 +2956,7 @@
         <v>3.42</v>
       </c>
       <c r="AA16">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB16">
         <v>1.91</v>
@@ -3409,10 +3409,10 @@
         <v>2.7</v>
       </c>
       <c r="O19">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="P19">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -3424,7 +3424,7 @@
         <v>1.49</v>
       </c>
       <c r="T19">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="U19">
         <v>3.4</v>
@@ -3445,13 +3445,13 @@
         <v>2.7</v>
       </c>
       <c r="AA19">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AB19">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AC19">
-        <v>4.28</v>
+        <v>4.4</v>
       </c>
       <c r="AD19">
         <v>1.19</v>
@@ -3575,7 +3575,7 @@
         <v>3.42</v>
       </c>
       <c r="P20">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -3599,13 +3599,13 @@
         <v>1.03</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y20">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Z20">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="AA20">
         <v>2.25</v>
@@ -3617,10 +3617,10 @@
         <v>4.45</v>
       </c>
       <c r="AD20">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE20">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AF20">
         <v>2.15</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AK20">
         <v>1.91</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="N13">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="O13">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="P13">
         <v>1.4</v>
@@ -2443,7 +2443,7 @@
         <v>2.62</v>
       </c>
       <c r="S13">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T13">
         <v>3.85</v>
@@ -2476,7 +2476,7 @@
         <v>2.09</v>
       </c>
       <c r="AD13">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AE13">
         <v>1.24</v>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="O19">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="P19">
         <v>2.4</v>
@@ -3421,19 +3421,19 @@
         <v>2.09</v>
       </c>
       <c r="S19">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T19">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="U19">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V19">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W19">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
         <v>1.02</v>
@@ -3448,10 +3448,10 @@
         <v>2.17</v>
       </c>
       <c r="AB19">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AC19">
-        <v>4.4</v>
+        <v>4.28</v>
       </c>
       <c r="AD19">
         <v>1.19</v>
@@ -3608,13 +3608,13 @@
         <v>2.47</v>
       </c>
       <c r="AA20">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AB20">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AC20">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AD20">
         <v>1.15</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AK20">
         <v>1.91</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -964,10 +964,10 @@
         <v>2.04</v>
       </c>
       <c r="O4">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P4">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="Q4">
         <v>2.28</v>
@@ -1009,7 +1009,7 @@
         <v>1.74</v>
       </c>
       <c r="AD4">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AE4">
         <v>1.45</v>
@@ -1018,7 +1018,7 @@
         <v>1.3</v>
       </c>
       <c r="AG4">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1619,13 +1619,13 @@
         <v>3.5</v>
       </c>
       <c r="P8">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q8">
         <v>4.02</v>
       </c>
       <c r="R8">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="S8">
         <v>1.22</v>
@@ -1655,7 +1655,7 @@
         <v>1.53</v>
       </c>
       <c r="AB8">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC8">
         <v>2.35</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="O9">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P9">
-        <v>4.48</v>
+        <v>4.5</v>
       </c>
       <c r="Q9">
         <v>2.21</v>
@@ -1815,10 +1815,10 @@
         <v>4.85</v>
       </c>
       <c r="AA9">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AB9">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="AC9">
         <v>2.26</v>
@@ -1942,7 +1942,7 @@
         <v>1.88</v>
       </c>
       <c r="O10">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
         <v>3.7</v>
@@ -1981,7 +1981,7 @@
         <v>1.76</v>
       </c>
       <c r="AB10">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AC10">
         <v>2.69</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="O11">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q11">
         <v>3.36</v>
       </c>
       <c r="R11">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="S11">
         <v>1.25</v>
       </c>
       <c r="T11">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="U11">
         <v>2.38</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="O12">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="Q12">
         <v>3.8</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="AK12">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3104,7 +3104,7 @@
         <v>2.8</v>
       </c>
       <c r="V17">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
         <v>1.05</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU24"/>
+  <dimension ref="A1:AU23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1082,22 +1082,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Widad Témara</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Widad Témara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK6">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-10-02 15:30:00</t>
+          <t>2026-10-02 15:00:00</t>
         </is>
       </c>
     </row>
@@ -1403,27 +1403,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.25</v>
+        <v>2.45</v>
       </c>
       <c r="O7">
+        <v>3</v>
+      </c>
+      <c r="P7">
+        <v>2.69</v>
+      </c>
+      <c r="Q7">
+        <v>3.34</v>
+      </c>
+      <c r="R7">
+        <v>1.98</v>
+      </c>
+      <c r="S7">
+        <v>1.4</v>
+      </c>
+      <c r="T7">
+        <v>2.75</v>
+      </c>
+      <c r="U7">
+        <v>3</v>
+      </c>
+      <c r="V7">
+        <v>1.35</v>
+      </c>
+      <c r="W7">
+        <v>1.07</v>
+      </c>
+      <c r="X7">
+        <v>1.02</v>
+      </c>
+      <c r="Y7">
+        <v>1.37</v>
+      </c>
+      <c r="Z7">
+        <v>3.06</v>
+      </c>
+      <c r="AA7">
+        <v>2.06</v>
+      </c>
+      <c r="AB7">
+        <v>1.68</v>
+      </c>
+      <c r="AC7">
         <v>3.5</v>
       </c>
-      <c r="P7">
-        <v>2.02</v>
-      </c>
-      <c r="Q7">
-        <v>3.8</v>
-      </c>
-      <c r="R7">
-        <v>2.48</v>
-      </c>
-      <c r="S7">
-        <v>1.25</v>
-      </c>
-      <c r="T7">
-        <v>3.6</v>
-      </c>
-      <c r="U7">
-        <v>2.25</v>
-      </c>
-      <c r="V7">
-        <v>1.57</v>
-      </c>
-      <c r="W7">
-        <v>1.11</v>
-      </c>
-      <c r="X7">
-        <v>1.01</v>
-      </c>
-      <c r="Y7">
-        <v>1.14</v>
-      </c>
-      <c r="Z7">
-        <v>4.88</v>
-      </c>
-      <c r="AA7">
-        <v>1.57</v>
-      </c>
-      <c r="AB7">
-        <v>2.38</v>
-      </c>
-      <c r="AC7">
-        <v>2.42</v>
-      </c>
       <c r="AD7">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="AE7">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AF7">
-        <v>1.48</v>
+        <v>1.83</v>
       </c>
       <c r="AG7">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AK7">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-10-02 15:45:00</t>
+          <t>2026-10-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,25 +1613,25 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q8">
-        <v>4.02</v>
+        <v>3.8</v>
       </c>
       <c r="R8">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="S8">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T8">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U8">
         <v>2.25</v>
@@ -1640,38 +1640,38 @@
         <v>1.57</v>
       </c>
       <c r="W8">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z8">
-        <v>4.68</v>
+        <v>4.88</v>
       </c>
       <c r="AA8">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB8">
+        <v>2.38</v>
+      </c>
+      <c r="AC8">
+        <v>2.42</v>
+      </c>
+      <c r="AD8">
+        <v>1.56</v>
+      </c>
+      <c r="AE8">
+        <v>1.22</v>
+      </c>
+      <c r="AF8">
+        <v>1.48</v>
+      </c>
+      <c r="AG8">
         <v>2.45</v>
       </c>
-      <c r="AC8">
-        <v>2.35</v>
-      </c>
-      <c r="AD8">
-        <v>1.58</v>
-      </c>
-      <c r="AE8">
-        <v>1.21</v>
-      </c>
-      <c r="AF8">
-        <v>1.5</v>
-      </c>
-      <c r="AG8">
-        <v>2.4</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.19</v>
+        <v>1.8</v>
       </c>
       <c r="AK8">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,31 +1776,31 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.61</v>
+        <v>3.1</v>
       </c>
       <c r="O9">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>4.5</v>
+        <v>1.95</v>
       </c>
       <c r="Q9">
-        <v>2.21</v>
+        <v>4.02</v>
       </c>
       <c r="R9">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="S9">
         <v>1.22</v>
       </c>
       <c r="T9">
-        <v>3.56</v>
+        <v>3.75</v>
       </c>
       <c r="U9">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V9">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W9">
         <v>1.14</v>
@@ -1809,31 +1809,31 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z9">
-        <v>4.85</v>
+        <v>4.68</v>
       </c>
       <c r="AA9">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB9">
+        <v>2.45</v>
+      </c>
+      <c r="AC9">
         <v>2.35</v>
       </c>
-      <c r="AC9">
-        <v>2.26</v>
-      </c>
       <c r="AD9">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AE9">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AF9">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG9">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AK9">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,65 +1939,65 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.88</v>
+        <v>1.61</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P10">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q10">
+        <v>2.21</v>
+      </c>
+      <c r="R10">
+        <v>2.5</v>
+      </c>
+      <c r="S10">
+        <v>1.22</v>
+      </c>
+      <c r="T10">
+        <v>3.56</v>
+      </c>
+      <c r="U10">
+        <v>2.15</v>
+      </c>
+      <c r="V10">
+        <v>1.58</v>
+      </c>
+      <c r="W10">
+        <v>1.14</v>
+      </c>
+      <c r="X10">
+        <v>1.01</v>
+      </c>
+      <c r="Y10">
+        <v>1.13</v>
+      </c>
+      <c r="Z10">
+        <v>4.85</v>
+      </c>
+      <c r="AA10">
+        <v>1.57</v>
+      </c>
+      <c r="AB10">
+        <v>2.35</v>
+      </c>
+      <c r="AC10">
+        <v>2.26</v>
+      </c>
+      <c r="AD10">
+        <v>1.63</v>
+      </c>
+      <c r="AE10">
+        <v>1.23</v>
+      </c>
+      <c r="AF10">
+        <v>1.55</v>
+      </c>
+      <c r="AG10">
         <v>2.3</v>
       </c>
-      <c r="R10">
-        <v>2.38</v>
-      </c>
-      <c r="S10">
-        <v>1.3</v>
-      </c>
-      <c r="T10">
-        <v>3.12</v>
-      </c>
-      <c r="U10">
-        <v>2.61</v>
-      </c>
-      <c r="V10">
-        <v>1.44</v>
-      </c>
-      <c r="W10">
-        <v>1.11</v>
-      </c>
-      <c r="X10">
-        <v>1.03</v>
-      </c>
-      <c r="Y10">
-        <v>1.21</v>
-      </c>
-      <c r="Z10">
-        <v>3.92</v>
-      </c>
-      <c r="AA10">
-        <v>1.76</v>
-      </c>
-      <c r="AB10">
-        <v>2.07</v>
-      </c>
-      <c r="AC10">
-        <v>2.69</v>
-      </c>
-      <c r="AD10">
-        <v>1.44</v>
-      </c>
-      <c r="AE10">
-        <v>1.13</v>
-      </c>
-      <c r="AF10">
-        <v>1.65</v>
-      </c>
-      <c r="AG10">
-        <v>2.08</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AK10">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.7</v>
+        <v>1.88</v>
       </c>
       <c r="O11">
         <v>3.4</v>
       </c>
       <c r="P11">
-        <v>2.12</v>
+        <v>3.7</v>
       </c>
       <c r="Q11">
-        <v>3.36</v>
+        <v>2.3</v>
       </c>
       <c r="R11">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="S11">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="U11">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
       <c r="V11">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z11">
-        <v>4.41</v>
+        <v>3.92</v>
       </c>
       <c r="AA11">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="AB11">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="AC11">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="AD11">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE11">
         <v>1.13</v>
       </c>
       <c r="AF11">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AG11">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK11">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="O12">
         <v>3.4</v>
       </c>
       <c r="P12">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="Q12">
-        <v>3.8</v>
+        <v>3.36</v>
       </c>
       <c r="R12">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="S12">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T12">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="U12">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V12">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z12">
-        <v>3.9</v>
+        <v>4.41</v>
       </c>
       <c r="AA12">
-        <v>1.83</v>
+        <v>1.59</v>
       </c>
       <c r="AB12">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="AC12">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AD12">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE12">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF12">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG12">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.61</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2381,27 +2381,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,81 +2428,81 @@
         </is>
       </c>
       <c r="N13">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="O13">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="P13">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="Q13">
-        <v>5.97</v>
+        <v>3.8</v>
       </c>
       <c r="R13">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="S13">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="U13">
+        <v>2.5</v>
+      </c>
+      <c r="V13">
+        <v>1.46</v>
+      </c>
+      <c r="W13">
+        <v>1.11</v>
+      </c>
+      <c r="X13">
+        <v>1.03</v>
+      </c>
+      <c r="Y13">
+        <v>1.23</v>
+      </c>
+      <c r="Z13">
+        <v>3.9</v>
+      </c>
+      <c r="AA13">
+        <v>1.83</v>
+      </c>
+      <c r="AB13">
+        <v>2.03</v>
+      </c>
+      <c r="AC13">
+        <v>2.7</v>
+      </c>
+      <c r="AD13">
+        <v>1.44</v>
+      </c>
+      <c r="AE13">
+        <v>1.15</v>
+      </c>
+      <c r="AF13">
+        <v>1.62</v>
+      </c>
+      <c r="AG13">
         <v>2.1</v>
       </c>
-      <c r="V13">
-        <v>1.65</v>
-      </c>
-      <c r="W13">
-        <v>1.14</v>
-      </c>
-      <c r="X13">
-        <v>1.02</v>
-      </c>
-      <c r="Y13">
-        <v>1.14</v>
-      </c>
-      <c r="Z13">
-        <v>5.75</v>
-      </c>
-      <c r="AA13">
-        <v>1.4</v>
-      </c>
-      <c r="AB13">
-        <v>2.75</v>
-      </c>
-      <c r="AC13">
-        <v>2.09</v>
-      </c>
-      <c r="AD13">
-        <v>1.68</v>
-      </c>
-      <c r="AE13">
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>1.61</v>
+      </c>
+      <c r="AK13">
         <v>1.24</v>
       </c>
-      <c r="AF13">
-        <v>1.59</v>
-      </c>
-      <c r="AG13">
-        <v>2.18</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.17</v>
-      </c>
-      <c r="AK13">
-        <v>1.1</v>
-      </c>
       <c r="AL13">
         <v>0</v>
       </c>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-10-02 16:00:00</t>
+          <t>2026-10-02 15:45:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Moghreb Tétouan</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>5.97</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-10-02 17:00:00</t>
+          <t>2026-10-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -2707,27 +2707,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Moghreb Tétouan</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>5.62</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK15">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-10-02 19:00:00</t>
+          <t>2026-10-02 17:00:00</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,80 +3732,80 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.26</v>
+        <v>4.06</v>
       </c>
       <c r="O21">
-        <v>2.8</v>
+        <v>3.64</v>
       </c>
       <c r="P21">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="Q21">
-        <v>3.04</v>
+        <v>3.64</v>
       </c>
       <c r="R21">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="S21">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="T21">
-        <v>2.22</v>
+        <v>3.6</v>
       </c>
       <c r="U21">
-        <v>3.58</v>
+        <v>2.29</v>
       </c>
       <c r="V21">
+        <v>1.61</v>
+      </c>
+      <c r="W21">
+        <v>1.12</v>
+      </c>
+      <c r="X21">
+        <v>1.02</v>
+      </c>
+      <c r="Y21">
+        <v>1.16</v>
+      </c>
+      <c r="Z21">
+        <v>4.3</v>
+      </c>
+      <c r="AA21">
+        <v>1.47</v>
+      </c>
+      <c r="AB21">
+        <v>2.3</v>
+      </c>
+      <c r="AC21">
+        <v>2.39</v>
+      </c>
+      <c r="AD21">
+        <v>1.46</v>
+      </c>
+      <c r="AE21">
+        <v>1.13</v>
+      </c>
+      <c r="AF21">
+        <v>1.51</v>
+      </c>
+      <c r="AG21">
+        <v>2.29</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>1.22</v>
+      </c>
+      <c r="AK21">
         <v>1.25</v>
-      </c>
-      <c r="W21">
-        <v>1.04</v>
-      </c>
-      <c r="X21">
-        <v>1.06</v>
-      </c>
-      <c r="Y21">
-        <v>1.49</v>
-      </c>
-      <c r="Z21">
-        <v>2.38</v>
-      </c>
-      <c r="AA21">
-        <v>2.87</v>
-      </c>
-      <c r="AB21">
-        <v>1.4</v>
-      </c>
-      <c r="AC21">
-        <v>4.98</v>
-      </c>
-      <c r="AD21">
-        <v>1.11</v>
-      </c>
-      <c r="AE21">
-        <v>1.04</v>
-      </c>
-      <c r="AF21">
-        <v>2.1</v>
-      </c>
-      <c r="AG21">
-        <v>1.64</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.3</v>
-      </c>
-      <c r="AK21">
-        <v>1.57</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>4.06</v>
+        <v>1.82</v>
       </c>
       <c r="O22">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="Q22">
-        <v>3.62</v>
+        <v>2.4</v>
       </c>
       <c r="R22">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S22">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="T22">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="U22">
-        <v>2.25</v>
+        <v>2.92</v>
       </c>
       <c r="V22">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="W22">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X22">
+        <v>1.01</v>
+      </c>
+      <c r="Y22">
+        <v>1.31</v>
+      </c>
+      <c r="Z22">
+        <v>2.92</v>
+      </c>
+      <c r="AA22">
+        <v>2.09</v>
+      </c>
+      <c r="AB22">
+        <v>1.68</v>
+      </c>
+      <c r="AC22">
+        <v>3.74</v>
+      </c>
+      <c r="AD22">
+        <v>1.19</v>
+      </c>
+      <c r="AE22">
         <v>1.02</v>
       </c>
-      <c r="Y22">
-        <v>1.13</v>
-      </c>
-      <c r="Z22">
-        <v>4.3</v>
-      </c>
-      <c r="AA22">
-        <v>1.46</v>
-      </c>
-      <c r="AB22">
-        <v>2.32</v>
-      </c>
-      <c r="AC22">
-        <v>2.44</v>
-      </c>
-      <c r="AD22">
-        <v>1.47</v>
-      </c>
-      <c r="AE22">
-        <v>1.13</v>
-      </c>
       <c r="AF22">
-        <v>1.4</v>
+        <v>1.93</v>
       </c>
       <c r="AG22">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK22">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-10-02 21:00:00</t>
+          <t>2026-10-02 21:35:00</t>
         </is>
       </c>
     </row>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.82</v>
+        <v>2.44</v>
       </c>
       <c r="O23">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="P23">
-        <v>4.6</v>
+        <v>2.54</v>
       </c>
       <c r="Q23">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="R23">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T23">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="U23">
-        <v>2.92</v>
+        <v>2.37</v>
       </c>
       <c r="V23">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="W23">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="Z23">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="AA23">
-        <v>2.09</v>
+        <v>1.61</v>
       </c>
       <c r="AB23">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="AC23">
-        <v>3.74</v>
+        <v>2.53</v>
       </c>
       <c r="AD23">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="AE23">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AF23">
-        <v>1.93</v>
+        <v>1.5</v>
       </c>
       <c r="AG23">
-        <v>1.78</v>
+        <v>2.38</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK23">
-        <v>1.94</v>
+        <v>1.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4161,169 +4161,6 @@
         <v>0</v>
       </c>
       <c r="AU23" t="inlineStr">
-        <is>
-          <t>2026-10-02 21:35:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Seattle Reign</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>North Carolina Courage</t>
-        </is>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N24">
-        <v>2.44</v>
-      </c>
-      <c r="O24">
-        <v>3.26</v>
-      </c>
-      <c r="P24">
-        <v>2.54</v>
-      </c>
-      <c r="Q24">
-        <v>3.1</v>
-      </c>
-      <c r="R24">
-        <v>2.3</v>
-      </c>
-      <c r="S24">
-        <v>1.25</v>
-      </c>
-      <c r="T24">
-        <v>3.4</v>
-      </c>
-      <c r="U24">
-        <v>2.37</v>
-      </c>
-      <c r="V24">
-        <v>1.55</v>
-      </c>
-      <c r="W24">
-        <v>1.12</v>
-      </c>
-      <c r="X24">
-        <v>1.03</v>
-      </c>
-      <c r="Y24">
-        <v>1.15</v>
-      </c>
-      <c r="Z24">
-        <v>4.2</v>
-      </c>
-      <c r="AA24">
-        <v>1.61</v>
-      </c>
-      <c r="AB24">
-        <v>2.25</v>
-      </c>
-      <c r="AC24">
-        <v>2.53</v>
-      </c>
-      <c r="AD24">
-        <v>1.47</v>
-      </c>
-      <c r="AE24">
-        <v>1.15</v>
-      </c>
-      <c r="AF24">
-        <v>1.5</v>
-      </c>
-      <c r="AG24">
-        <v>2.38</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.3</v>
-      </c>
-      <c r="AK24">
-        <v>1.4</v>
-      </c>
-      <c r="AL24">
-        <v>0</v>
-      </c>
-      <c r="AM24">
-        <v>-1</v>
-      </c>
-      <c r="AN24">
-        <v>-1</v>
-      </c>
-      <c r="AO24">
-        <v>-1</v>
-      </c>
-      <c r="AP24">
-        <v>-1</v>
-      </c>
-      <c r="AQ24">
-        <v>0</v>
-      </c>
-      <c r="AR24">
-        <v>0</v>
-      </c>
-      <c r="AS24">
-        <v>0</v>
-      </c>
-      <c r="AT24">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
         <is>
           <t>2026-10-02 23:00:00</t>
         </is>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -964,22 +964,22 @@
         <v>2.04</v>
       </c>
       <c r="O4">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P4">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="Q4">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="R4">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="S4">
         <v>1.17</v>
       </c>
       <c r="T4">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="U4">
         <v>1.96</v>
@@ -988,7 +988,7 @@
         <v>1.86</v>
       </c>
       <c r="W4">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X4">
         <v>1.01</v>
@@ -997,28 +997,28 @@
         <v>1.06</v>
       </c>
       <c r="Z4">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB4">
         <v>3.4</v>
       </c>
       <c r="AC4">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AD4">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AE4">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AF4">
         <v>1.3</v>
       </c>
       <c r="AG4">
-        <v>3.32</v>
+        <v>3.14</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O7">
         <v>3</v>
       </c>
       <c r="P7">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="Q7">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="R7">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="S7">
         <v>1.4</v>
@@ -1471,43 +1471,43 @@
         <v>2.75</v>
       </c>
       <c r="U7">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V7">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W7">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
         <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z7">
-        <v>3.06</v>
+        <v>2.96</v>
       </c>
       <c r="AA7">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AB7">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC7">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AD7">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE7">
         <v>1.04</v>
       </c>
       <c r="AF7">
+        <v>1.85</v>
+      </c>
+      <c r="AG7">
         <v>1.83</v>
-      </c>
-      <c r="AG7">
-        <v>1.85</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1622,16 +1622,16 @@
         <v>2</v>
       </c>
       <c r="Q8">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="R8">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="S8">
         <v>1.25</v>
       </c>
       <c r="T8">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="U8">
         <v>2.25</v>
@@ -1640,16 +1640,16 @@
         <v>1.57</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z8">
-        <v>4.88</v>
+        <v>4.9</v>
       </c>
       <c r="AA8">
         <v>1.57</v>
@@ -1658,7 +1658,7 @@
         <v>2.38</v>
       </c>
       <c r="AC8">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="AD8">
         <v>1.56</v>
@@ -1667,7 +1667,7 @@
         <v>1.22</v>
       </c>
       <c r="AF8">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AG8">
         <v>2.45</v>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O9">
         <v>3.5</v>
       </c>
       <c r="P9">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="Q9">
-        <v>4.02</v>
+        <v>3.94</v>
       </c>
       <c r="R9">
         <v>2.28</v>
@@ -1818,13 +1818,13 @@
         <v>1.53</v>
       </c>
       <c r="AB9">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AC9">
         <v>2.35</v>
       </c>
       <c r="AD9">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE9">
         <v>1.21</v>
@@ -1945,10 +1945,10 @@
         <v>3.8</v>
       </c>
       <c r="P10">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q10">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="R10">
         <v>2.5</v>
@@ -1978,7 +1978,7 @@
         <v>4.85</v>
       </c>
       <c r="AA10">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AB10">
         <v>2.35</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="O12">
         <v>3.4</v>
       </c>
       <c r="P12">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
       <c r="Q12">
-        <v>3.36</v>
+        <v>3.8</v>
       </c>
       <c r="R12">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="S12">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V12">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="W12">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z12">
-        <v>4.41</v>
+        <v>3.9</v>
       </c>
       <c r="AA12">
-        <v>1.59</v>
+        <v>1.83</v>
       </c>
       <c r="AB12">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="AC12">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AD12">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE12">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF12">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AG12">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>1.61</v>
       </c>
       <c r="AK12">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="O13">
         <v>3.4</v>
       </c>
       <c r="P13">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="Q13">
-        <v>3.8</v>
+        <v>3.36</v>
       </c>
       <c r="R13">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="S13">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T13">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="U13">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V13">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z13">
-        <v>3.9</v>
+        <v>4.41</v>
       </c>
       <c r="AA13">
-        <v>1.83</v>
+        <v>1.59</v>
       </c>
       <c r="AB13">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="AC13">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AD13">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE13">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF13">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG13">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.61</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2929,7 +2929,7 @@
         <v>2.88</v>
       </c>
       <c r="R16">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="S16">
         <v>1.38</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK16">
         <v>1.53</v>
@@ -3128,7 +3128,7 @@
         <v>3.42</v>
       </c>
       <c r="AD17">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE17">
         <v>1.04</v>
@@ -3252,13 +3252,13 @@
         <v>3.3</v>
       </c>
       <c r="Q18">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="R18">
         <v>2.2</v>
       </c>
       <c r="S18">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T18">
         <v>3.1</v>
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="O19">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P19">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q19">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="R19">
         <v>2.09</v>
@@ -3439,7 +3439,7 @@
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Z19">
         <v>2.7</v>
@@ -3451,10 +3451,10 @@
         <v>1.61</v>
       </c>
       <c r="AC19">
-        <v>4.28</v>
+        <v>4.4</v>
       </c>
       <c r="AD19">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE19">
         <v>1.01</v>
@@ -3479,7 +3479,7 @@
         <v>1.31</v>
       </c>
       <c r="AK19">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3575,7 +3575,7 @@
         <v>3.42</v>
       </c>
       <c r="P20">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="Q20">
         <v>2.3</v>
@@ -3599,13 +3599,13 @@
         <v>1.03</v>
       </c>
       <c r="X20">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Z20">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AA20">
         <v>2.38</v>
@@ -3620,7 +3620,7 @@
         <v>1.15</v>
       </c>
       <c r="AE20">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AF20">
         <v>2.15</v>
@@ -3741,22 +3741,22 @@
         <v>1.7</v>
       </c>
       <c r="Q21">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="R21">
         <v>2.15</v>
       </c>
       <c r="S21">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="T21">
         <v>3.6</v>
       </c>
       <c r="U21">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="V21">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="W21">
         <v>1.12</v>
@@ -3765,19 +3765,19 @@
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z21">
         <v>4.3</v>
       </c>
       <c r="AA21">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB21">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="AC21">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
       <c r="AD21">
         <v>1.46</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -3409,7 +3409,7 @@
         <v>2.87</v>
       </c>
       <c r="O19">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="P19">
         <v>2.25</v>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="O20">
-        <v>3.42</v>
+        <v>3.56</v>
       </c>
       <c r="P20">
         <v>4.33</v>
@@ -3602,7 +3602,7 @@
         <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Z20">
         <v>2.5</v>
@@ -3617,10 +3617,10 @@
         <v>4.5</v>
       </c>
       <c r="AD20">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE20">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF20">
         <v>2.15</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="O3">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q3">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="R3">
+        <v>2.15</v>
+      </c>
+      <c r="S3">
+        <v>1.42</v>
+      </c>
+      <c r="T3">
+        <v>2.78</v>
+      </c>
+      <c r="U3">
+        <v>2.84</v>
+      </c>
+      <c r="V3">
+        <v>1.38</v>
+      </c>
+      <c r="W3">
+        <v>1.04</v>
+      </c>
+      <c r="X3">
+        <v>1.03</v>
+      </c>
+      <c r="Y3">
+        <v>1.3</v>
+      </c>
+      <c r="Z3">
+        <v>3.3</v>
+      </c>
+      <c r="AA3">
         <v>2</v>
       </c>
-      <c r="S3">
-        <v>1.36</v>
-      </c>
-      <c r="T3">
-        <v>2.88</v>
-      </c>
-      <c r="U3">
-        <v>3</v>
-      </c>
-      <c r="V3">
-        <v>1.33</v>
-      </c>
-      <c r="W3">
-        <v>1.05</v>
-      </c>
-      <c r="X3">
-        <v>1</v>
-      </c>
-      <c r="Y3">
-        <v>1.33</v>
-      </c>
-      <c r="Z3">
-        <v>3.14</v>
-      </c>
-      <c r="AA3">
-        <v>2.07</v>
-      </c>
       <c r="AB3">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AC3">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="AD3">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE3">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AG3">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AK3">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="O4">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P4">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="Q4">
         <v>2.16</v>
@@ -1006,13 +1006,13 @@
         <v>3.4</v>
       </c>
       <c r="AC4">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AD4">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AE4">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AF4">
         <v>1.3</v>
@@ -1450,25 +1450,25 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O7">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P7">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="Q7">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R7">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="S7">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T7">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U7">
         <v>3.1</v>
@@ -1480,34 +1480,34 @@
         <v>1.06</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z7">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="AA7">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="AB7">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AC7">
-        <v>3.58</v>
+        <v>3.88</v>
       </c>
       <c r="AD7">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE7">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF7">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AG7">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.4</v>
       </c>
       <c r="AK7">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O8">
         <v>3.4</v>
@@ -1655,7 +1655,7 @@
         <v>1.57</v>
       </c>
       <c r="AB8">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="AC8">
         <v>2.41</v>
@@ -1670,7 +1670,7 @@
         <v>1.49</v>
       </c>
       <c r="AG8">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>3.5</v>
       </c>
       <c r="P9">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="Q9">
         <v>3.94</v>
@@ -1797,7 +1797,7 @@
         <v>3.75</v>
       </c>
       <c r="U9">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V9">
         <v>1.57</v>
@@ -1812,22 +1812,22 @@
         <v>1.16</v>
       </c>
       <c r="Z9">
-        <v>4.68</v>
+        <v>4.57</v>
       </c>
       <c r="AA9">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB9">
         <v>2.35</v>
       </c>
       <c r="AC9">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AD9">
         <v>1.56</v>
       </c>
       <c r="AE9">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF9">
         <v>1.5</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,7 +1948,7 @@
         <v>4.2</v>
       </c>
       <c r="Q10">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="R10">
         <v>2.5</v>
@@ -1957,13 +1957,13 @@
         <v>1.22</v>
       </c>
       <c r="T10">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="U10">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V10">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W10">
         <v>1.14</v>
@@ -1972,22 +1972,22 @@
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z10">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="AA10">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AB10">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AC10">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AD10">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AE10">
         <v>1.23</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK10">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="O11">
         <v>3.4</v>
       </c>
       <c r="P11">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q11">
         <v>2.3</v>
@@ -2135,16 +2135,16 @@
         <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="AA11">
         <v>1.76</v>
       </c>
       <c r="AB11">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC11">
         <v>2.69</v>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O12">
-        <v>3.4</v>
+        <v>3.96</v>
       </c>
       <c r="P12">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="Q12">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="R12">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
         <v>1.3</v>
@@ -2301,16 +2301,16 @@
         <v>1.23</v>
       </c>
       <c r="Z12">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="AA12">
         <v>1.83</v>
       </c>
       <c r="AB12">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AC12">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AD12">
         <v>1.44</v>
@@ -2319,7 +2319,7 @@
         <v>1.15</v>
       </c>
       <c r="AF12">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG12">
         <v>2.1</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="O13">
         <v>3.4</v>
       </c>
       <c r="P13">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="Q13">
         <v>3.36</v>
@@ -2464,7 +2464,7 @@
         <v>1.16</v>
       </c>
       <c r="Z13">
-        <v>4.41</v>
+        <v>4.43</v>
       </c>
       <c r="AA13">
         <v>1.59</v>
@@ -2594,7 +2594,7 @@
         <v>5.5</v>
       </c>
       <c r="O14">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="P14">
         <v>1.4</v>
@@ -2621,7 +2621,7 @@
         <v>1.14</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
         <v>1.14</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK16">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3412,7 +3412,7 @@
         <v>2.98</v>
       </c>
       <c r="P19">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q19">
         <v>3.66</v>
@@ -3439,7 +3439,7 @@
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z19">
         <v>2.7</v>
@@ -3774,10 +3774,10 @@
         <v>1.46</v>
       </c>
       <c r="AB21">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="AC21">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="AD21">
         <v>1.46</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="O3">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q3">
         <v>2.8</v>
@@ -1082,22 +1082,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Widad Témara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC5">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK5">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Widad Témara</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-10-02 15:00:00</t>
+          <t>2026-10-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -1403,27 +1403,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="O7">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
-        <v>2.73</v>
+        <v>2</v>
       </c>
       <c r="Q7">
-        <v>3.35</v>
+        <v>3.87</v>
       </c>
       <c r="R7">
-        <v>1.94</v>
+        <v>2.49</v>
       </c>
       <c r="S7">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>2.63</v>
+        <v>3.36</v>
       </c>
       <c r="U7">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="V7">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.43</v>
+        <v>1.13</v>
       </c>
       <c r="Z7">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="AA7">
-        <v>2.19</v>
+        <v>1.57</v>
       </c>
       <c r="AB7">
-        <v>1.59</v>
+        <v>2.21</v>
       </c>
       <c r="AC7">
-        <v>3.88</v>
+        <v>2.41</v>
       </c>
       <c r="AD7">
-        <v>1.21</v>
+        <v>1.56</v>
       </c>
       <c r="AE7">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="AF7">
-        <v>1.93</v>
+        <v>1.49</v>
       </c>
       <c r="AG7">
-        <v>1.78</v>
+        <v>2.44</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AK7">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-10-02 15:30:00</t>
+          <t>2026-10-02 15:45:00</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q8">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="R8">
-        <v>2.49</v>
+        <v>2.28</v>
       </c>
       <c r="S8">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T8">
-        <v>3.36</v>
+        <v>3.75</v>
       </c>
       <c r="U8">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V8">
         <v>1.57</v>
       </c>
       <c r="W8">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X8">
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z8">
-        <v>4.9</v>
+        <v>4.57</v>
       </c>
       <c r="AA8">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB8">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="AC8">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="AD8">
         <v>1.56</v>
       </c>
       <c r="AE8">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF8">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG8">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,28 +1776,28 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.3</v>
+        <v>1.61</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P9">
-        <v>2.02</v>
+        <v>4.2</v>
       </c>
       <c r="Q9">
-        <v>3.94</v>
+        <v>2.26</v>
       </c>
       <c r="R9">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="S9">
         <v>1.22</v>
       </c>
       <c r="T9">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="U9">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V9">
         <v>1.57</v>
@@ -1809,31 +1809,31 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z9">
-        <v>4.57</v>
+        <v>4.8</v>
       </c>
       <c r="AA9">
+        <v>1.56</v>
+      </c>
+      <c r="AB9">
+        <v>2.43</v>
+      </c>
+      <c r="AC9">
+        <v>2.3</v>
+      </c>
+      <c r="AD9">
+        <v>1.53</v>
+      </c>
+      <c r="AE9">
+        <v>1.23</v>
+      </c>
+      <c r="AF9">
         <v>1.55</v>
       </c>
-      <c r="AB9">
-        <v>2.35</v>
-      </c>
-      <c r="AC9">
-        <v>2.39</v>
-      </c>
-      <c r="AD9">
-        <v>1.56</v>
-      </c>
-      <c r="AE9">
-        <v>1.2</v>
-      </c>
-      <c r="AF9">
-        <v>1.5</v>
-      </c>
       <c r="AG9">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK9">
-        <v>1.29</v>
+        <v>2.1</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.61</v>
+        <v>1.89</v>
       </c>
       <c r="O10">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="Q10">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R10">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S10">
+        <v>1.3</v>
+      </c>
+      <c r="T10">
+        <v>3.12</v>
+      </c>
+      <c r="U10">
+        <v>2.61</v>
+      </c>
+      <c r="V10">
+        <v>1.44</v>
+      </c>
+      <c r="W10">
+        <v>1.11</v>
+      </c>
+      <c r="X10">
+        <v>1.03</v>
+      </c>
+      <c r="Y10">
         <v>1.22</v>
       </c>
-      <c r="T10">
-        <v>3.54</v>
-      </c>
-      <c r="U10">
-        <v>2.25</v>
-      </c>
-      <c r="V10">
-        <v>1.57</v>
-      </c>
-      <c r="W10">
-        <v>1.14</v>
-      </c>
-      <c r="X10">
-        <v>1.01</v>
-      </c>
-      <c r="Y10">
-        <v>1.14</v>
-      </c>
       <c r="Z10">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA10">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="AB10">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="AC10">
-        <v>2.3</v>
+        <v>2.69</v>
       </c>
       <c r="AD10">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE10">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG10">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AK10">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,31 +2102,31 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.89</v>
+        <v>3.45</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.96</v>
       </c>
       <c r="P11">
-        <v>3.75</v>
+        <v>1.91</v>
       </c>
       <c r="Q11">
-        <v>2.3</v>
+        <v>3.94</v>
       </c>
       <c r="R11">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S11">
         <v>1.3</v>
       </c>
       <c r="T11">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U11">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="V11">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W11">
         <v>1.11</v>
@@ -2135,13 +2135,13 @@
         <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z11">
-        <v>4.1</v>
+        <v>3.93</v>
       </c>
       <c r="AA11">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AB11">
         <v>2.05</v>
@@ -2153,13 +2153,13 @@
         <v>1.44</v>
       </c>
       <c r="AE11">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG11">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.19</v>
+        <v>1.61</v>
       </c>
       <c r="AK11">
-        <v>1.91</v>
+        <v>1.24</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="O12">
-        <v>3.96</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
-        <v>1.91</v>
+        <v>2.24</v>
       </c>
       <c r="Q12">
-        <v>3.94</v>
+        <v>3.36</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="S12">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T12">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="U12">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V12">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z12">
-        <v>3.93</v>
+        <v>4.43</v>
       </c>
       <c r="AA12">
-        <v>1.83</v>
+        <v>1.59</v>
       </c>
       <c r="AB12">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AC12">
-        <v>2.69</v>
+        <v>2.49</v>
       </c>
       <c r="AD12">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE12">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF12">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="AG12">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.61</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2381,27 +2381,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="O13">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="P13">
-        <v>2.24</v>
+        <v>1.4</v>
       </c>
       <c r="Q13">
-        <v>3.36</v>
+        <v>5.97</v>
       </c>
       <c r="R13">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="S13">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T13">
-        <v>3.38</v>
+        <v>3.85</v>
       </c>
       <c r="U13">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="V13">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="W13">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z13">
-        <v>4.43</v>
+        <v>5.75</v>
       </c>
       <c r="AA13">
+        <v>1.4</v>
+      </c>
+      <c r="AB13">
+        <v>2.75</v>
+      </c>
+      <c r="AC13">
+        <v>2.09</v>
+      </c>
+      <c r="AD13">
+        <v>1.68</v>
+      </c>
+      <c r="AE13">
+        <v>1.24</v>
+      </c>
+      <c r="AF13">
         <v>1.59</v>
       </c>
-      <c r="AB13">
-        <v>2.17</v>
-      </c>
-      <c r="AC13">
-        <v>2.49</v>
-      </c>
-      <c r="AD13">
-        <v>1.42</v>
-      </c>
-      <c r="AE13">
-        <v>1.13</v>
-      </c>
-      <c r="AF13">
-        <v>1.52</v>
-      </c>
       <c r="AG13">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK13">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-10-02 15:45:00</t>
+          <t>2026-10-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Moghreb Tétouan</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>5.97</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-10-02 16:00:00</t>
+          <t>2026-10-02 17:00:00</t>
         </is>
       </c>
     </row>
@@ -2707,27 +2707,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Moghreb Tétouan</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-10-02 17:00:00</t>
+          <t>2026-10-02 19:00:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -801,10 +801,10 @@
         <v>2.3</v>
       </c>
       <c r="O3">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q3">
         <v>2.8</v>
@@ -816,7 +816,7 @@
         <v>1.42</v>
       </c>
       <c r="T3">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="U3">
         <v>2.84</v>
@@ -825,22 +825,22 @@
         <v>1.38</v>
       </c>
       <c r="W3">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X3">
         <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z3">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA3">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB3">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC3">
         <v>3.22</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK3">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1320,31 +1320,31 @@
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="Z6">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AA6">
         <v>2.19</v>
       </c>
       <c r="AB6">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AC6">
         <v>3.88</v>
       </c>
       <c r="AD6">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE6">
         <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG6">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="N13">
-        <v>5.5</v>
+        <v>6.51</v>
       </c>
       <c r="O13">
-        <v>5.2</v>
+        <v>4.85</v>
       </c>
       <c r="P13">
         <v>1.4</v>
       </c>
       <c r="Q13">
-        <v>5.97</v>
+        <v>4.45</v>
       </c>
       <c r="R13">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="S13">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T13">
         <v>3.85</v>
       </c>
       <c r="U13">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="V13">
         <v>1.65</v>
@@ -2470,22 +2470,22 @@
         <v>1.4</v>
       </c>
       <c r="AB13">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC13">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AD13">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AE13">
         <v>1.24</v>
       </c>
       <c r="AF13">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG13">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK13">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2971,10 +2971,10 @@
         <v>1.08</v>
       </c>
       <c r="AF16">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.87</v>
+        <v>3.15</v>
       </c>
       <c r="O19">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="P19">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="Q19">
         <v>3.66</v>
@@ -3424,7 +3424,7 @@
         <v>1.48</v>
       </c>
       <c r="T19">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="U19">
         <v>3.3</v>
@@ -3448,10 +3448,10 @@
         <v>2.17</v>
       </c>
       <c r="AB19">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC19">
-        <v>4.4</v>
+        <v>4.34</v>
       </c>
       <c r="AD19">
         <v>1.2</v>
@@ -3460,10 +3460,10 @@
         <v>1.01</v>
       </c>
       <c r="AF19">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG19">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="O20">
         <v>3.56</v>
@@ -3608,7 +3608,7 @@
         <v>2.5</v>
       </c>
       <c r="AA20">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AB20">
         <v>1.59</v>
@@ -3642,7 +3642,7 @@
         <v>1.28</v>
       </c>
       <c r="AK20">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL20">
         <v>0</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -961,31 +961,31 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="O4">
-        <v>4.5</v>
+        <v>3.73</v>
       </c>
       <c r="P4">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="Q4">
         <v>2.16</v>
       </c>
       <c r="R4">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="S4">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="U4">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="V4">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="W4">
         <v>1.24</v>
@@ -1006,16 +1006,16 @@
         <v>3.4</v>
       </c>
       <c r="AC4">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AD4">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AE4">
         <v>1.4</v>
       </c>
       <c r="AF4">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AG4">
         <v>3.14</v>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK4">
         <v>1.7</v>
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.05</v>
+        <v>3.21</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q7">
-        <v>3.87</v>
+        <v>3.56</v>
       </c>
       <c r="R7">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="S7">
         <v>1.25</v>
@@ -1486,28 +1486,28 @@
         <v>1.13</v>
       </c>
       <c r="Z7">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AA7">
         <v>1.57</v>
       </c>
       <c r="AB7">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="AC7">
-        <v>2.41</v>
+        <v>2.32</v>
       </c>
       <c r="AD7">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AE7">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF7">
         <v>1.49</v>
       </c>
       <c r="AG7">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,28 +1613,28 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.3</v>
+        <v>1.61</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P8">
-        <v>2.02</v>
+        <v>4.2</v>
       </c>
       <c r="Q8">
-        <v>3.94</v>
+        <v>2.26</v>
       </c>
       <c r="R8">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="S8">
         <v>1.22</v>
       </c>
       <c r="T8">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="U8">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V8">
         <v>1.57</v>
@@ -1646,31 +1646,31 @@
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z8">
-        <v>4.57</v>
+        <v>4.8</v>
       </c>
       <c r="AA8">
+        <v>1.53</v>
+      </c>
+      <c r="AB8">
+        <v>2.37</v>
+      </c>
+      <c r="AC8">
+        <v>2.3</v>
+      </c>
+      <c r="AD8">
+        <v>1.53</v>
+      </c>
+      <c r="AE8">
+        <v>1.23</v>
+      </c>
+      <c r="AF8">
         <v>1.55</v>
       </c>
-      <c r="AB8">
-        <v>2.35</v>
-      </c>
-      <c r="AC8">
-        <v>2.39</v>
-      </c>
-      <c r="AD8">
-        <v>1.56</v>
-      </c>
-      <c r="AE8">
-        <v>1.2</v>
-      </c>
-      <c r="AF8">
-        <v>1.5</v>
-      </c>
       <c r="AG8">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK8">
-        <v>1.29</v>
+        <v>2.1</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,58 +1776,58 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.61</v>
+        <v>2.9</v>
       </c>
       <c r="O9">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>4.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q9">
-        <v>2.26</v>
+        <v>3.36</v>
       </c>
       <c r="R9">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="S9">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T9">
-        <v>3.54</v>
+        <v>3.38</v>
       </c>
       <c r="U9">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V9">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W9">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z9">
-        <v>4.8</v>
+        <v>4.48</v>
       </c>
       <c r="AA9">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AB9">
-        <v>2.43</v>
+        <v>2.17</v>
       </c>
       <c r="AC9">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="AD9">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AE9">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AF9">
         <v>1.55</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1945,7 +1945,7 @@
         <v>3.4</v>
       </c>
       <c r="P10">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q10">
         <v>2.3</v>
@@ -1960,7 +1960,7 @@
         <v>3.12</v>
       </c>
       <c r="U10">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="V10">
         <v>1.44</v>
@@ -1981,7 +1981,7 @@
         <v>1.76</v>
       </c>
       <c r="AB10">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC10">
         <v>2.69</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="O11">
-        <v>3.96</v>
+        <v>3.75</v>
       </c>
       <c r="P11">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q11">
         <v>3.94</v>
@@ -2129,7 +2129,7 @@
         <v>1.46</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X11">
         <v>1.03</v>
@@ -2141,10 +2141,10 @@
         <v>3.93</v>
       </c>
       <c r="AA11">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB11">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC11">
         <v>2.69</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AK11">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="O12">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>2.24</v>
+        <v>1.97</v>
       </c>
       <c r="Q12">
-        <v>3.36</v>
+        <v>3.29</v>
       </c>
       <c r="R12">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="S12">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T12">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="U12">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="V12">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W12">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X12">
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z12">
-        <v>4.43</v>
+        <v>4.57</v>
       </c>
       <c r="AA12">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AB12">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="AC12">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="AD12">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AE12">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF12">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG12">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="AK12">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3131,10 +3131,10 @@
         <v>1.25</v>
       </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF17">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG17">
         <v>1.81</v>
@@ -3246,7 +3246,7 @@
         <v>2.05</v>
       </c>
       <c r="O18">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
         <v>3.3</v>
@@ -3747,7 +3747,7 @@
         <v>2.15</v>
       </c>
       <c r="S21">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
         <v>3.6</v>
@@ -3774,7 +3774,7 @@
         <v>1.46</v>
       </c>
       <c r="AB21">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="AC21">
         <v>2.33</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.9</v>
+        <v>1.89</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P9">
-        <v>2.24</v>
+        <v>3.6</v>
       </c>
       <c r="Q9">
-        <v>3.36</v>
+        <v>2.3</v>
       </c>
       <c r="R9">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S9">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T9">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="U9">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="V9">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>4.48</v>
+        <v>4.1</v>
       </c>
       <c r="AA9">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="AB9">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="AC9">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="AD9">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE9">
         <v>1.13</v>
       </c>
       <c r="AF9">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG9">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK9">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.89</v>
+        <v>2.9</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P10">
-        <v>3.6</v>
+        <v>2.24</v>
       </c>
       <c r="Q10">
-        <v>2.3</v>
+        <v>3.36</v>
       </c>
       <c r="R10">
+        <v>2.2</v>
+      </c>
+      <c r="S10">
+        <v>1.29</v>
+      </c>
+      <c r="T10">
+        <v>3.38</v>
+      </c>
+      <c r="U10">
         <v>2.38</v>
       </c>
-      <c r="S10">
-        <v>1.3</v>
-      </c>
-      <c r="T10">
-        <v>3.12</v>
-      </c>
-      <c r="U10">
-        <v>2.63</v>
-      </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z10">
-        <v>4.1</v>
+        <v>4.48</v>
       </c>
       <c r="AA10">
-        <v>1.76</v>
+        <v>1.59</v>
       </c>
       <c r="AB10">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="AC10">
-        <v>2.69</v>
+        <v>2.49</v>
       </c>
       <c r="AD10">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE10">
         <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AG10">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="AL10">
         <v>0</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.89</v>
+        <v>3.1</v>
       </c>
       <c r="O9">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>3.6</v>
+        <v>1.97</v>
       </c>
       <c r="Q9">
-        <v>2.3</v>
+        <v>3.29</v>
       </c>
       <c r="R9">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="S9">
+        <v>1.22</v>
+      </c>
+      <c r="T9">
+        <v>3.75</v>
+      </c>
+      <c r="U9">
+        <v>2.29</v>
+      </c>
+      <c r="V9">
+        <v>1.57</v>
+      </c>
+      <c r="W9">
+        <v>1.14</v>
+      </c>
+      <c r="X9">
+        <v>1.01</v>
+      </c>
+      <c r="Y9">
+        <v>1.17</v>
+      </c>
+      <c r="Z9">
+        <v>4.57</v>
+      </c>
+      <c r="AA9">
+        <v>1.55</v>
+      </c>
+      <c r="AB9">
+        <v>2.35</v>
+      </c>
+      <c r="AC9">
+        <v>2.39</v>
+      </c>
+      <c r="AD9">
+        <v>1.55</v>
+      </c>
+      <c r="AE9">
+        <v>1.2</v>
+      </c>
+      <c r="AF9">
+        <v>1.5</v>
+      </c>
+      <c r="AG9">
+        <v>2.4</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>1.75</v>
+      </c>
+      <c r="AK9">
         <v>1.3</v>
-      </c>
-      <c r="T9">
-        <v>3.12</v>
-      </c>
-      <c r="U9">
-        <v>2.63</v>
-      </c>
-      <c r="V9">
-        <v>1.44</v>
-      </c>
-      <c r="W9">
-        <v>1.11</v>
-      </c>
-      <c r="X9">
-        <v>1.03</v>
-      </c>
-      <c r="Y9">
-        <v>1.22</v>
-      </c>
-      <c r="Z9">
-        <v>4.1</v>
-      </c>
-      <c r="AA9">
-        <v>1.76</v>
-      </c>
-      <c r="AB9">
-        <v>2.07</v>
-      </c>
-      <c r="AC9">
-        <v>2.69</v>
-      </c>
-      <c r="AD9">
-        <v>1.44</v>
-      </c>
-      <c r="AE9">
-        <v>1.13</v>
-      </c>
-      <c r="AF9">
-        <v>1.65</v>
-      </c>
-      <c r="AG9">
-        <v>2.08</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.19</v>
-      </c>
-      <c r="AK9">
-        <v>1.91</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.9</v>
+        <v>1.89</v>
       </c>
       <c r="O10">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>2.24</v>
+        <v>3.6</v>
       </c>
       <c r="Q10">
-        <v>3.36</v>
+        <v>2.3</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S10">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="U10">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="V10">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>4.48</v>
+        <v>4.1</v>
       </c>
       <c r="AA10">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="AB10">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="AC10">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="AD10">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE10">
         <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG10">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK10">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="O11">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P11">
-        <v>1.85</v>
+        <v>2.24</v>
       </c>
       <c r="Q11">
-        <v>3.94</v>
+        <v>3.36</v>
       </c>
       <c r="R11">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T11">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="U11">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V11">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W11">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z11">
-        <v>3.93</v>
+        <v>4.48</v>
       </c>
       <c r="AA11">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AB11">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AC11">
-        <v>2.69</v>
+        <v>2.49</v>
       </c>
       <c r="AD11">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE11">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF11">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AG11">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="AK11">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,80 +2265,80 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P12">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="Q12">
-        <v>3.29</v>
+        <v>3.94</v>
       </c>
       <c r="R12">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
+        <v>1.3</v>
+      </c>
+      <c r="T12">
+        <v>3.2</v>
+      </c>
+      <c r="U12">
+        <v>2.5</v>
+      </c>
+      <c r="V12">
+        <v>1.46</v>
+      </c>
+      <c r="W12">
+        <v>1.1</v>
+      </c>
+      <c r="X12">
+        <v>1.03</v>
+      </c>
+      <c r="Y12">
+        <v>1.23</v>
+      </c>
+      <c r="Z12">
+        <v>3.93</v>
+      </c>
+      <c r="AA12">
+        <v>1.8</v>
+      </c>
+      <c r="AB12">
+        <v>2</v>
+      </c>
+      <c r="AC12">
+        <v>2.69</v>
+      </c>
+      <c r="AD12">
+        <v>1.44</v>
+      </c>
+      <c r="AE12">
+        <v>1.15</v>
+      </c>
+      <c r="AF12">
+        <v>1.63</v>
+      </c>
+      <c r="AG12">
+        <v>2.1</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <v>1.64</v>
+      </c>
+      <c r="AK12">
         <v>1.22</v>
-      </c>
-      <c r="T12">
-        <v>3.75</v>
-      </c>
-      <c r="U12">
-        <v>2.29</v>
-      </c>
-      <c r="V12">
-        <v>1.57</v>
-      </c>
-      <c r="W12">
-        <v>1.14</v>
-      </c>
-      <c r="X12">
-        <v>1.01</v>
-      </c>
-      <c r="Y12">
-        <v>1.17</v>
-      </c>
-      <c r="Z12">
-        <v>4.57</v>
-      </c>
-      <c r="AA12">
-        <v>1.55</v>
-      </c>
-      <c r="AB12">
-        <v>2.35</v>
-      </c>
-      <c r="AC12">
-        <v>2.39</v>
-      </c>
-      <c r="AD12">
-        <v>1.55</v>
-      </c>
-      <c r="AE12">
-        <v>1.2</v>
-      </c>
-      <c r="AF12">
-        <v>1.5</v>
-      </c>
-      <c r="AG12">
-        <v>2.4</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.75</v>
-      </c>
-      <c r="AK12">
-        <v>1.3</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2956,7 +2956,7 @@
         <v>3.42</v>
       </c>
       <c r="AA16">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB16">
         <v>1.91</v>
@@ -3412,7 +3412,7 @@
         <v>3.25</v>
       </c>
       <c r="P19">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q19">
         <v>3.66</v>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="O20">
         <v>3.56</v>
@@ -3590,7 +3590,7 @@
         <v>2.55</v>
       </c>
       <c r="U20">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V20">
         <v>1.3</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -638,10 +638,10 @@
         <v>1.63</v>
       </c>
       <c r="O2">
-        <v>3.35</v>
+        <v>3.78</v>
       </c>
       <c r="P2">
-        <v>4.81</v>
+        <v>4.75</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -831,16 +831,16 @@
         <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z3">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA3">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB3">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AC3">
         <v>3.22</v>
@@ -1127,22 +1127,22 @@
         <v>2.6</v>
       </c>
       <c r="O5">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="P5">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="Q5">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="R5">
         <v>1.83</v>
       </c>
       <c r="S5">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="T5">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="U5">
         <v>4</v>
@@ -1157,19 +1157,19 @@
         <v>1.1</v>
       </c>
       <c r="Y5">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Z5">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="AA5">
-        <v>2.89</v>
+        <v>2.71</v>
       </c>
       <c r="AB5">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AC5">
-        <v>5.05</v>
+        <v>5.15</v>
       </c>
       <c r="AD5">
         <v>1.1</v>
@@ -1178,7 +1178,7 @@
         <v>1.01</v>
       </c>
       <c r="AF5">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AG5">
         <v>1.73</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AK5">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1293,55 +1293,55 @@
         <v>2.9</v>
       </c>
       <c r="P6">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="Q6">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="R6">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="S6">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T6">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U6">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="V6">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W6">
         <v>1.06</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="Z6">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="AA6">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="AB6">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AC6">
-        <v>3.88</v>
+        <v>4.2</v>
       </c>
       <c r="AD6">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE6">
         <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG6">
         <v>1.73</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P9">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="Q9">
-        <v>3.29</v>
+        <v>3.94</v>
       </c>
       <c r="R9">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="S9">
+        <v>1.3</v>
+      </c>
+      <c r="T9">
+        <v>3.2</v>
+      </c>
+      <c r="U9">
+        <v>2.5</v>
+      </c>
+      <c r="V9">
+        <v>1.46</v>
+      </c>
+      <c r="W9">
+        <v>1.1</v>
+      </c>
+      <c r="X9">
+        <v>1.03</v>
+      </c>
+      <c r="Y9">
+        <v>1.23</v>
+      </c>
+      <c r="Z9">
+        <v>3.93</v>
+      </c>
+      <c r="AA9">
+        <v>1.8</v>
+      </c>
+      <c r="AB9">
+        <v>2</v>
+      </c>
+      <c r="AC9">
+        <v>2.69</v>
+      </c>
+      <c r="AD9">
+        <v>1.44</v>
+      </c>
+      <c r="AE9">
+        <v>1.15</v>
+      </c>
+      <c r="AF9">
+        <v>1.63</v>
+      </c>
+      <c r="AG9">
+        <v>2.1</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>1.64</v>
+      </c>
+      <c r="AK9">
         <v>1.22</v>
-      </c>
-      <c r="T9">
-        <v>3.75</v>
-      </c>
-      <c r="U9">
-        <v>2.29</v>
-      </c>
-      <c r="V9">
-        <v>1.57</v>
-      </c>
-      <c r="W9">
-        <v>1.14</v>
-      </c>
-      <c r="X9">
-        <v>1.01</v>
-      </c>
-      <c r="Y9">
-        <v>1.17</v>
-      </c>
-      <c r="Z9">
-        <v>4.57</v>
-      </c>
-      <c r="AA9">
-        <v>1.55</v>
-      </c>
-      <c r="AB9">
-        <v>2.35</v>
-      </c>
-      <c r="AC9">
-        <v>2.39</v>
-      </c>
-      <c r="AD9">
-        <v>1.55</v>
-      </c>
-      <c r="AE9">
-        <v>1.2</v>
-      </c>
-      <c r="AF9">
-        <v>1.5</v>
-      </c>
-      <c r="AG9">
-        <v>2.4</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.75</v>
-      </c>
-      <c r="AK9">
-        <v>1.3</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.89</v>
+        <v>2.9</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P10">
-        <v>3.6</v>
+        <v>2.24</v>
       </c>
       <c r="Q10">
-        <v>2.3</v>
+        <v>3.36</v>
       </c>
       <c r="R10">
+        <v>2.2</v>
+      </c>
+      <c r="S10">
+        <v>1.29</v>
+      </c>
+      <c r="T10">
+        <v>3.38</v>
+      </c>
+      <c r="U10">
         <v>2.38</v>
       </c>
-      <c r="S10">
-        <v>1.3</v>
-      </c>
-      <c r="T10">
-        <v>3.12</v>
-      </c>
-      <c r="U10">
-        <v>2.63</v>
-      </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z10">
-        <v>4.1</v>
+        <v>4.48</v>
       </c>
       <c r="AA10">
-        <v>1.76</v>
+        <v>1.59</v>
       </c>
       <c r="AB10">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="AC10">
-        <v>2.69</v>
+        <v>2.49</v>
       </c>
       <c r="AD10">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE10">
         <v>1.13</v>
       </c>
       <c r="AF10">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AG10">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.9</v>
+        <v>1.89</v>
       </c>
       <c r="O11">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>2.24</v>
+        <v>3.6</v>
       </c>
       <c r="Q11">
-        <v>3.36</v>
+        <v>2.3</v>
       </c>
       <c r="R11">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S11">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="U11">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="V11">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z11">
-        <v>4.48</v>
+        <v>4.1</v>
       </c>
       <c r="AA11">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="AB11">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="AC11">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="AD11">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE11">
         <v>1.13</v>
       </c>
       <c r="AF11">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG11">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK11">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,80 +2265,80 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O12">
+        <v>3.5</v>
+      </c>
+      <c r="P12">
+        <v>1.97</v>
+      </c>
+      <c r="Q12">
+        <v>3.29</v>
+      </c>
+      <c r="R12">
+        <v>2.28</v>
+      </c>
+      <c r="S12">
+        <v>1.22</v>
+      </c>
+      <c r="T12">
         <v>3.75</v>
       </c>
-      <c r="P12">
-        <v>1.85</v>
-      </c>
-      <c r="Q12">
-        <v>3.94</v>
-      </c>
-      <c r="R12">
-        <v>2.25</v>
-      </c>
-      <c r="S12">
+      <c r="U12">
+        <v>2.29</v>
+      </c>
+      <c r="V12">
+        <v>1.57</v>
+      </c>
+      <c r="W12">
+        <v>1.14</v>
+      </c>
+      <c r="X12">
+        <v>1.01</v>
+      </c>
+      <c r="Y12">
+        <v>1.17</v>
+      </c>
+      <c r="Z12">
+        <v>4.57</v>
+      </c>
+      <c r="AA12">
+        <v>1.55</v>
+      </c>
+      <c r="AB12">
+        <v>2.35</v>
+      </c>
+      <c r="AC12">
+        <v>2.39</v>
+      </c>
+      <c r="AD12">
+        <v>1.55</v>
+      </c>
+      <c r="AE12">
+        <v>1.2</v>
+      </c>
+      <c r="AF12">
+        <v>1.5</v>
+      </c>
+      <c r="AG12">
+        <v>2.4</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <v>1.75</v>
+      </c>
+      <c r="AK12">
         <v>1.3</v>
-      </c>
-      <c r="T12">
-        <v>3.2</v>
-      </c>
-      <c r="U12">
-        <v>2.5</v>
-      </c>
-      <c r="V12">
-        <v>1.46</v>
-      </c>
-      <c r="W12">
-        <v>1.1</v>
-      </c>
-      <c r="X12">
-        <v>1.03</v>
-      </c>
-      <c r="Y12">
-        <v>1.23</v>
-      </c>
-      <c r="Z12">
-        <v>3.93</v>
-      </c>
-      <c r="AA12">
-        <v>1.8</v>
-      </c>
-      <c r="AB12">
-        <v>2</v>
-      </c>
-      <c r="AC12">
-        <v>2.69</v>
-      </c>
-      <c r="AD12">
-        <v>1.44</v>
-      </c>
-      <c r="AE12">
-        <v>1.15</v>
-      </c>
-      <c r="AF12">
-        <v>1.63</v>
-      </c>
-      <c r="AG12">
-        <v>2.1</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.64</v>
-      </c>
-      <c r="AK12">
-        <v>1.22</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>6.51</v>
+        <v>6.5</v>
       </c>
       <c r="O13">
-        <v>4.85</v>
+        <v>4.6</v>
       </c>
       <c r="P13">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Q13">
         <v>4.45</v>
@@ -2446,46 +2446,46 @@
         <v>1.2</v>
       </c>
       <c r="T13">
-        <v>3.85</v>
+        <v>3.96</v>
       </c>
       <c r="U13">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="V13">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="W13">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z13">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA13">
         <v>1.4</v>
       </c>
       <c r="AB13">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC13">
         <v>2.1</v>
       </c>
       <c r="AD13">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AE13">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF13">
         <v>1.62</v>
       </c>
       <c r="AG13">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O14">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P14">
-        <v>4.13</v>
+        <v>4.3</v>
       </c>
       <c r="Q14">
         <v>2.5</v>
@@ -2642,7 +2642,7 @@
         <v>1.14</v>
       </c>
       <c r="AE14">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AF14">
         <v>2.15</v>
@@ -2664,7 +2664,7 @@
         <v>1.14</v>
       </c>
       <c r="AK14">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="O16">
         <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="Q16">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R16">
         <v>2.15</v>
@@ -2938,10 +2938,10 @@
         <v>3</v>
       </c>
       <c r="U16">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="V16">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W16">
         <v>1.06</v>
@@ -2956,13 +2956,13 @@
         <v>3.42</v>
       </c>
       <c r="AA16">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB16">
         <v>1.91</v>
       </c>
       <c r="AC16">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="AD16">
         <v>1.34</v>
@@ -2990,7 +2990,7 @@
         <v>1.3</v>
       </c>
       <c r="AK16">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O19">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="Q19">
         <v>3.66</v>
@@ -3421,19 +3421,19 @@
         <v>2.09</v>
       </c>
       <c r="S19">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="T19">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="U19">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V19">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X19">
         <v>1.02</v>
@@ -3451,7 +3451,7 @@
         <v>1.62</v>
       </c>
       <c r="AC19">
-        <v>4.34</v>
+        <v>4.4</v>
       </c>
       <c r="AD19">
         <v>1.2</v>
@@ -3590,7 +3590,7 @@
         <v>2.55</v>
       </c>
       <c r="U20">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V20">
         <v>1.3</v>
@@ -3605,10 +3605,10 @@
         <v>1.47</v>
       </c>
       <c r="Z20">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AA20">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB20">
         <v>1.59</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -964,22 +964,22 @@
         <v>2.07</v>
       </c>
       <c r="O4">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="P4">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q4">
         <v>2.16</v>
       </c>
       <c r="R4">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="S4">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="T4">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="U4">
         <v>1.99</v>
@@ -988,37 +988,37 @@
         <v>1.83</v>
       </c>
       <c r="W4">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z4">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AB4">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC4">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AD4">
         <v>1.89</v>
       </c>
       <c r="AE4">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AF4">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AG4">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="O7">
         <v>3.5</v>
       </c>
       <c r="P7">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="Q7">
         <v>3.56</v>
       </c>
       <c r="R7">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="S7">
         <v>1.25</v>
@@ -1486,16 +1486,16 @@
         <v>1.13</v>
       </c>
       <c r="Z7">
-        <v>4.95</v>
+        <v>5.02</v>
       </c>
       <c r="AA7">
         <v>1.57</v>
       </c>
       <c r="AB7">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AC7">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="AD7">
         <v>1.52</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AK7">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.61</v>
+        <v>3.6</v>
       </c>
       <c r="O8">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="P8">
-        <v>4.2</v>
+        <v>1.9</v>
       </c>
       <c r="Q8">
-        <v>2.26</v>
+        <v>3.9</v>
       </c>
       <c r="R8">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S8">
+        <v>1.4</v>
+      </c>
+      <c r="T8">
+        <v>2.88</v>
+      </c>
+      <c r="U8">
+        <v>2.9</v>
+      </c>
+      <c r="V8">
+        <v>1.35</v>
+      </c>
+      <c r="W8">
+        <v>1.06</v>
+      </c>
+      <c r="X8">
+        <v>1.03</v>
+      </c>
+      <c r="Y8">
+        <v>1.36</v>
+      </c>
+      <c r="Z8">
+        <v>2.75</v>
+      </c>
+      <c r="AA8">
+        <v>2.05</v>
+      </c>
+      <c r="AB8">
+        <v>1.75</v>
+      </c>
+      <c r="AC8">
+        <v>3.29</v>
+      </c>
+      <c r="AD8">
+        <v>1.3</v>
+      </c>
+      <c r="AE8">
+        <v>1.16</v>
+      </c>
+      <c r="AF8">
+        <v>1.83</v>
+      </c>
+      <c r="AG8">
+        <v>1.8</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <v>1.64</v>
+      </c>
+      <c r="AK8">
         <v>1.22</v>
-      </c>
-      <c r="T8">
-        <v>3.54</v>
-      </c>
-      <c r="U8">
-        <v>2.25</v>
-      </c>
-      <c r="V8">
-        <v>1.57</v>
-      </c>
-      <c r="W8">
-        <v>1.14</v>
-      </c>
-      <c r="X8">
-        <v>1.01</v>
-      </c>
-      <c r="Y8">
-        <v>1.14</v>
-      </c>
-      <c r="Z8">
-        <v>4.8</v>
-      </c>
-      <c r="AA8">
-        <v>1.53</v>
-      </c>
-      <c r="AB8">
-        <v>2.37</v>
-      </c>
-      <c r="AC8">
-        <v>2.3</v>
-      </c>
-      <c r="AD8">
-        <v>1.53</v>
-      </c>
-      <c r="AE8">
-        <v>1.23</v>
-      </c>
-      <c r="AF8">
-        <v>1.55</v>
-      </c>
-      <c r="AG8">
-        <v>2.3</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.14</v>
-      </c>
-      <c r="AK8">
-        <v>2.1</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="O9">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>1.85</v>
+        <v>2.24</v>
       </c>
       <c r="Q9">
-        <v>3.94</v>
+        <v>3.36</v>
       </c>
       <c r="R9">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S9">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T9">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="U9">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V9">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W9">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z9">
-        <v>3.93</v>
+        <v>4.53</v>
       </c>
       <c r="AA9">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AB9">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AC9">
-        <v>2.69</v>
+        <v>2.49</v>
       </c>
       <c r="AD9">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE9">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF9">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AG9">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.9</v>
+        <v>1.75</v>
       </c>
       <c r="O10">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P10">
-        <v>2.24</v>
+        <v>4.1</v>
       </c>
       <c r="Q10">
-        <v>3.36</v>
+        <v>2.3</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S10">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="U10">
-        <v>2.38</v>
+        <v>2.59</v>
       </c>
       <c r="V10">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>4.48</v>
+        <v>4.33</v>
       </c>
       <c r="AA10">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="AB10">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="AC10">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="AD10">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE10">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF10">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG10">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK10">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.89</v>
+        <v>3.3</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P11">
-        <v>3.6</v>
+        <v>1.93</v>
       </c>
       <c r="Q11">
-        <v>2.3</v>
+        <v>3.29</v>
       </c>
       <c r="R11">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="S11">
+        <v>1.22</v>
+      </c>
+      <c r="T11">
+        <v>3.75</v>
+      </c>
+      <c r="U11">
+        <v>2.29</v>
+      </c>
+      <c r="V11">
+        <v>1.57</v>
+      </c>
+      <c r="W11">
+        <v>1.14</v>
+      </c>
+      <c r="X11">
+        <v>1.01</v>
+      </c>
+      <c r="Y11">
+        <v>1.17</v>
+      </c>
+      <c r="Z11">
+        <v>4.57</v>
+      </c>
+      <c r="AA11">
+        <v>1.55</v>
+      </c>
+      <c r="AB11">
+        <v>2.35</v>
+      </c>
+      <c r="AC11">
+        <v>2.39</v>
+      </c>
+      <c r="AD11">
+        <v>1.54</v>
+      </c>
+      <c r="AE11">
+        <v>1.2</v>
+      </c>
+      <c r="AF11">
+        <v>1.5</v>
+      </c>
+      <c r="AG11">
+        <v>2.4</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>1.75</v>
+      </c>
+      <c r="AK11">
         <v>1.3</v>
-      </c>
-      <c r="T11">
-        <v>3.12</v>
-      </c>
-      <c r="U11">
-        <v>2.63</v>
-      </c>
-      <c r="V11">
-        <v>1.44</v>
-      </c>
-      <c r="W11">
-        <v>1.11</v>
-      </c>
-      <c r="X11">
-        <v>1.03</v>
-      </c>
-      <c r="Y11">
-        <v>1.22</v>
-      </c>
-      <c r="Z11">
-        <v>4.1</v>
-      </c>
-      <c r="AA11">
-        <v>1.76</v>
-      </c>
-      <c r="AB11">
-        <v>2.07</v>
-      </c>
-      <c r="AC11">
-        <v>2.69</v>
-      </c>
-      <c r="AD11">
-        <v>1.44</v>
-      </c>
-      <c r="AE11">
-        <v>1.13</v>
-      </c>
-      <c r="AF11">
-        <v>1.65</v>
-      </c>
-      <c r="AG11">
-        <v>2.08</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.19</v>
-      </c>
-      <c r="AK11">
-        <v>1.91</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,28 +2265,28 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P12">
-        <v>1.97</v>
+        <v>4</v>
       </c>
       <c r="Q12">
-        <v>3.29</v>
+        <v>2.26</v>
       </c>
       <c r="R12">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="S12">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T12">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="U12">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V12">
         <v>1.57</v>
@@ -2298,31 +2298,31 @@
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z12">
-        <v>4.57</v>
+        <v>4.8</v>
       </c>
       <c r="AA12">
+        <v>1.56</v>
+      </c>
+      <c r="AB12">
+        <v>2.46</v>
+      </c>
+      <c r="AC12">
+        <v>2.3</v>
+      </c>
+      <c r="AD12">
+        <v>1.53</v>
+      </c>
+      <c r="AE12">
+        <v>1.23</v>
+      </c>
+      <c r="AF12">
         <v>1.55</v>
       </c>
-      <c r="AB12">
-        <v>2.35</v>
-      </c>
-      <c r="AC12">
-        <v>2.39</v>
-      </c>
-      <c r="AD12">
-        <v>1.55</v>
-      </c>
-      <c r="AE12">
-        <v>1.2</v>
-      </c>
-      <c r="AF12">
-        <v>1.5</v>
-      </c>
       <c r="AG12">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.75</v>
+        <v>1.14</v>
       </c>
       <c r="AK12">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3098,7 +3098,7 @@
         <v>1.41</v>
       </c>
       <c r="T17">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="U17">
         <v>2.8</v>
@@ -3134,7 +3134,7 @@
         <v>1.1</v>
       </c>
       <c r="AF17">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG17">
         <v>1.81</v>
@@ -3252,13 +3252,13 @@
         <v>3.3</v>
       </c>
       <c r="Q18">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="R18">
         <v>2.2</v>
       </c>
       <c r="S18">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T18">
         <v>3.1</v>
@@ -3753,10 +3753,10 @@
         <v>3.6</v>
       </c>
       <c r="U21">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="V21">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W21">
         <v>1.12</v>
@@ -3771,10 +3771,10 @@
         <v>4.3</v>
       </c>
       <c r="AA21">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AB21">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AC21">
         <v>2.33</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.85</v>
+        <v>1.75</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P9">
-        <v>2.24</v>
+        <v>4.1</v>
       </c>
       <c r="Q9">
-        <v>3.36</v>
+        <v>2.3</v>
       </c>
       <c r="R9">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S9">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T9">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="U9">
-        <v>2.38</v>
+        <v>2.59</v>
       </c>
       <c r="V9">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>4.53</v>
+        <v>4.33</v>
       </c>
       <c r="AA9">
-        <v>1.59</v>
+        <v>1.74</v>
       </c>
       <c r="AB9">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="AC9">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="AD9">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE9">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG9">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK9">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,65 +1939,65 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.75</v>
+        <v>2.85</v>
       </c>
       <c r="O10">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P10">
-        <v>4.1</v>
+        <v>2.24</v>
       </c>
       <c r="Q10">
+        <v>3.36</v>
+      </c>
+      <c r="R10">
+        <v>2.2</v>
+      </c>
+      <c r="S10">
+        <v>1.29</v>
+      </c>
+      <c r="T10">
+        <v>3.38</v>
+      </c>
+      <c r="U10">
+        <v>2.38</v>
+      </c>
+      <c r="V10">
+        <v>1.53</v>
+      </c>
+      <c r="W10">
+        <v>1.12</v>
+      </c>
+      <c r="X10">
+        <v>1.01</v>
+      </c>
+      <c r="Y10">
+        <v>1.16</v>
+      </c>
+      <c r="Z10">
+        <v>4.53</v>
+      </c>
+      <c r="AA10">
+        <v>1.59</v>
+      </c>
+      <c r="AB10">
+        <v>2.17</v>
+      </c>
+      <c r="AC10">
+        <v>2.49</v>
+      </c>
+      <c r="AD10">
+        <v>1.42</v>
+      </c>
+      <c r="AE10">
+        <v>1.13</v>
+      </c>
+      <c r="AF10">
+        <v>1.55</v>
+      </c>
+      <c r="AG10">
         <v>2.3</v>
       </c>
-      <c r="R10">
-        <v>2.38</v>
-      </c>
-      <c r="S10">
-        <v>1.3</v>
-      </c>
-      <c r="T10">
-        <v>3.12</v>
-      </c>
-      <c r="U10">
-        <v>2.59</v>
-      </c>
-      <c r="V10">
-        <v>1.44</v>
-      </c>
-      <c r="W10">
-        <v>1.11</v>
-      </c>
-      <c r="X10">
-        <v>1.03</v>
-      </c>
-      <c r="Y10">
-        <v>1.2</v>
-      </c>
-      <c r="Z10">
-        <v>4.33</v>
-      </c>
-      <c r="AA10">
-        <v>1.74</v>
-      </c>
-      <c r="AB10">
-        <v>2.07</v>
-      </c>
-      <c r="AC10">
-        <v>2.69</v>
-      </c>
-      <c r="AD10">
-        <v>1.44</v>
-      </c>
-      <c r="AE10">
-        <v>1.14</v>
-      </c>
-      <c r="AF10">
-        <v>1.65</v>
-      </c>
-      <c r="AG10">
-        <v>2.08</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,28 +2102,28 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.3</v>
+        <v>1.65</v>
       </c>
       <c r="O11">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P11">
-        <v>1.93</v>
+        <v>4</v>
       </c>
       <c r="Q11">
-        <v>3.29</v>
+        <v>2.26</v>
       </c>
       <c r="R11">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="S11">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T11">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="U11">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="V11">
         <v>1.57</v>
@@ -2135,31 +2135,31 @@
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z11">
-        <v>4.57</v>
+        <v>4.8</v>
       </c>
       <c r="AA11">
+        <v>1.56</v>
+      </c>
+      <c r="AB11">
+        <v>2.46</v>
+      </c>
+      <c r="AC11">
+        <v>2.3</v>
+      </c>
+      <c r="AD11">
+        <v>1.53</v>
+      </c>
+      <c r="AE11">
+        <v>1.23</v>
+      </c>
+      <c r="AF11">
         <v>1.55</v>
       </c>
-      <c r="AB11">
-        <v>2.35</v>
-      </c>
-      <c r="AC11">
-        <v>2.39</v>
-      </c>
-      <c r="AD11">
-        <v>1.54</v>
-      </c>
-      <c r="AE11">
-        <v>1.2</v>
-      </c>
-      <c r="AF11">
-        <v>1.5</v>
-      </c>
       <c r="AG11">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.75</v>
+        <v>1.14</v>
       </c>
       <c r="AK11">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,28 +2265,28 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.65</v>
+        <v>3.3</v>
       </c>
       <c r="O12">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>4</v>
+        <v>1.93</v>
       </c>
       <c r="Q12">
-        <v>2.26</v>
+        <v>3.29</v>
       </c>
       <c r="R12">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="S12">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T12">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="U12">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V12">
         <v>1.57</v>
@@ -2298,31 +2298,31 @@
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z12">
-        <v>4.8</v>
+        <v>4.57</v>
       </c>
       <c r="AA12">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB12">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="AC12">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AD12">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE12">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AF12">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG12">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.14</v>
+        <v>1.75</v>
       </c>
       <c r="AK12">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="AL12">
         <v>0</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="O8">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>1.9</v>
+        <v>2.24</v>
       </c>
       <c r="Q8">
-        <v>3.9</v>
+        <v>3.36</v>
       </c>
       <c r="R8">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S8">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="T8">
-        <v>2.88</v>
+        <v>3.38</v>
       </c>
       <c r="U8">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="V8">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
+        <v>1.16</v>
+      </c>
+      <c r="Z8">
+        <v>4.53</v>
+      </c>
+      <c r="AA8">
+        <v>1.59</v>
+      </c>
+      <c r="AB8">
+        <v>2.17</v>
+      </c>
+      <c r="AC8">
+        <v>2.49</v>
+      </c>
+      <c r="AD8">
+        <v>1.42</v>
+      </c>
+      <c r="AE8">
+        <v>1.13</v>
+      </c>
+      <c r="AF8">
+        <v>1.55</v>
+      </c>
+      <c r="AG8">
+        <v>2.3</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <v>1.22</v>
+      </c>
+      <c r="AK8">
         <v>1.36</v>
-      </c>
-      <c r="Z8">
-        <v>2.75</v>
-      </c>
-      <c r="AA8">
-        <v>2.05</v>
-      </c>
-      <c r="AB8">
-        <v>1.75</v>
-      </c>
-      <c r="AC8">
-        <v>3.29</v>
-      </c>
-      <c r="AD8">
-        <v>1.3</v>
-      </c>
-      <c r="AE8">
-        <v>1.16</v>
-      </c>
-      <c r="AF8">
-        <v>1.83</v>
-      </c>
-      <c r="AG8">
-        <v>1.8</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.64</v>
-      </c>
-      <c r="AK8">
-        <v>1.22</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="O9">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P9">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="Q9">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="R9">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S9">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T9">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="U9">
-        <v>2.59</v>
+        <v>2.9</v>
       </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
         <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="Z9">
-        <v>4.33</v>
+        <v>2.75</v>
       </c>
       <c r="AA9">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="AB9">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AC9">
-        <v>2.69</v>
+        <v>3.29</v>
       </c>
       <c r="AD9">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AE9">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF9">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AG9">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.19</v>
+        <v>1.64</v>
       </c>
       <c r="AK9">
-        <v>2</v>
+        <v>1.22</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,58 +1939,58 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.85</v>
+        <v>1.65</v>
       </c>
       <c r="O10">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P10">
-        <v>2.24</v>
+        <v>4</v>
       </c>
       <c r="Q10">
-        <v>3.36</v>
+        <v>2.26</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S10">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T10">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="U10">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V10">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W10">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z10">
-        <v>4.53</v>
+        <v>4.8</v>
       </c>
       <c r="AA10">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AB10">
-        <v>2.17</v>
+        <v>2.46</v>
       </c>
       <c r="AC10">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AD10">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AE10">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AF10">
         <v>1.55</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK10">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
+        <v>1.75</v>
+      </c>
+      <c r="O11">
+        <v>3.6</v>
+      </c>
+      <c r="P11">
+        <v>4.1</v>
+      </c>
+      <c r="Q11">
+        <v>2.3</v>
+      </c>
+      <c r="R11">
+        <v>2.38</v>
+      </c>
+      <c r="S11">
+        <v>1.3</v>
+      </c>
+      <c r="T11">
+        <v>3.12</v>
+      </c>
+      <c r="U11">
+        <v>2.59</v>
+      </c>
+      <c r="V11">
+        <v>1.44</v>
+      </c>
+      <c r="W11">
+        <v>1.11</v>
+      </c>
+      <c r="X11">
+        <v>1.03</v>
+      </c>
+      <c r="Y11">
+        <v>1.2</v>
+      </c>
+      <c r="Z11">
+        <v>4.33</v>
+      </c>
+      <c r="AA11">
+        <v>1.74</v>
+      </c>
+      <c r="AB11">
+        <v>2.07</v>
+      </c>
+      <c r="AC11">
+        <v>2.69</v>
+      </c>
+      <c r="AD11">
+        <v>1.44</v>
+      </c>
+      <c r="AE11">
+        <v>1.14</v>
+      </c>
+      <c r="AF11">
         <v>1.65</v>
       </c>
-      <c r="O11">
-        <v>3.8</v>
-      </c>
-      <c r="P11">
-        <v>4</v>
-      </c>
-      <c r="Q11">
-        <v>2.26</v>
-      </c>
-      <c r="R11">
-        <v>2.5</v>
-      </c>
-      <c r="S11">
-        <v>1.25</v>
-      </c>
-      <c r="T11">
-        <v>3.54</v>
-      </c>
-      <c r="U11">
-        <v>2.25</v>
-      </c>
-      <c r="V11">
-        <v>1.57</v>
-      </c>
-      <c r="W11">
-        <v>1.14</v>
-      </c>
-      <c r="X11">
-        <v>1.01</v>
-      </c>
-      <c r="Y11">
-        <v>1.14</v>
-      </c>
-      <c r="Z11">
-        <v>4.8</v>
-      </c>
-      <c r="AA11">
-        <v>1.56</v>
-      </c>
-      <c r="AB11">
-        <v>2.46</v>
-      </c>
-      <c r="AC11">
-        <v>2.3</v>
-      </c>
-      <c r="AD11">
-        <v>1.53</v>
-      </c>
-      <c r="AE11">
-        <v>1.23</v>
-      </c>
-      <c r="AF11">
-        <v>1.55</v>
-      </c>
       <c r="AG11">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AK11">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL11">
         <v>0</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -627,72 +627,72 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
         <v>1.63</v>
       </c>
       <c r="O2">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="P2">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AA2">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AB2">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -701,41 +701,41 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57"]</t>
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -798,16 +798,16 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="O3">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P3">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="Q3">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="R3">
         <v>2.15</v>
@@ -819,10 +819,10 @@
         <v>2.62</v>
       </c>
       <c r="U3">
-        <v>2.84</v>
+        <v>2.71</v>
       </c>
       <c r="V3">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W3">
         <v>1.08</v>
@@ -837,10 +837,10 @@
         <v>3.3</v>
       </c>
       <c r="AA3">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AB3">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AC3">
         <v>3.22</v>
@@ -849,13 +849,13 @@
         <v>1.31</v>
       </c>
       <c r="AE3">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF3">
         <v>1.73</v>
       </c>
       <c r="AG3">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -938,57 +938,57 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="O4">
-        <v>3.7</v>
+        <v>4.66</v>
       </c>
       <c r="P4">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q4">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="R4">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="S4">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T4">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="U4">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="V4">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="W4">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X4">
         <v>1.01</v>
@@ -997,71 +997,71 @@
         <v>1.05</v>
       </c>
       <c r="Z4">
+        <v>8.5</v>
+      </c>
+      <c r="AA4">
+        <v>1.25</v>
+      </c>
+      <c r="AB4">
+        <v>3.6</v>
+      </c>
+      <c r="AC4">
+        <v>1.66</v>
+      </c>
+      <c r="AD4">
+        <v>2.21</v>
+      </c>
+      <c r="AE4">
+        <v>1.51</v>
+      </c>
+      <c r="AF4">
+        <v>1.29</v>
+      </c>
+      <c r="AG4">
+        <v>3.48</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>["4", "9", "13", "78", "86"]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
+        <v>1.29</v>
+      </c>
+      <c r="AK4">
+        <v>1.83</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
         <v>8</v>
       </c>
-      <c r="AA4">
-        <v>1.29</v>
-      </c>
-      <c r="AB4">
-        <v>3.5</v>
-      </c>
-      <c r="AC4">
-        <v>1.73</v>
-      </c>
-      <c r="AD4">
-        <v>1.89</v>
-      </c>
-      <c r="AE4">
-        <v>1.46</v>
-      </c>
-      <c r="AF4">
-        <v>1.3</v>
-      </c>
-      <c r="AG4">
-        <v>3.34</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.31</v>
-      </c>
-      <c r="AK4">
-        <v>1.7</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>-1</v>
-      </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1124,22 +1124,22 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="O5">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="P5">
         <v>3.1</v>
       </c>
       <c r="Q5">
-        <v>3.72</v>
+        <v>3.61</v>
       </c>
       <c r="R5">
         <v>1.83</v>
       </c>
       <c r="S5">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="T5">
         <v>2.02</v>
@@ -1157,19 +1157,19 @@
         <v>1.1</v>
       </c>
       <c r="Y5">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Z5">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="AA5">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="AB5">
         <v>1.44</v>
       </c>
       <c r="AC5">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="AD5">
         <v>1.1</v>
@@ -1178,7 +1178,7 @@
         <v>1.01</v>
       </c>
       <c r="AF5">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AG5">
         <v>1.73</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AK5">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,16 +1287,16 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="O6">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="P6">
-        <v>2.76</v>
+        <v>3.02</v>
       </c>
       <c r="Q6">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="R6">
         <v>1.9</v>
@@ -1308,25 +1308,25 @@
         <v>2.5</v>
       </c>
       <c r="U6">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V6">
         <v>1.3</v>
       </c>
       <c r="W6">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
         <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Z6">
         <v>2.72</v>
       </c>
       <c r="AA6">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AB6">
         <v>1.55</v>
@@ -1335,10 +1335,10 @@
         <v>4.2</v>
       </c>
       <c r="AD6">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE6">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF6">
         <v>2</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK6">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,25 +1613,25 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="O8">
         <v>3.5</v>
       </c>
       <c r="P8">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="Q8">
-        <v>3.36</v>
+        <v>3.56</v>
       </c>
       <c r="R8">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="S8">
         <v>1.29</v>
       </c>
       <c r="T8">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="U8">
         <v>2.38</v>
@@ -1649,13 +1649,13 @@
         <v>1.16</v>
       </c>
       <c r="Z8">
-        <v>4.53</v>
+        <v>4.61</v>
       </c>
       <c r="AA8">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AB8">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AC8">
         <v>2.49</v>
@@ -1664,7 +1664,7 @@
         <v>1.42</v>
       </c>
       <c r="AE8">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF8">
         <v>1.55</v>
@@ -1686,7 +1686,7 @@
         <v>1.22</v>
       </c>
       <c r="AK8">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.6</v>
+        <v>1.65</v>
       </c>
       <c r="O9">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="P9">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="Q9">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="R9">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="S9">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="T9">
-        <v>2.88</v>
+        <v>3.54</v>
       </c>
       <c r="U9">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="Z9">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA9">
-        <v>2.05</v>
+        <v>1.56</v>
       </c>
       <c r="AB9">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="AC9">
-        <v>3.29</v>
+        <v>2.3</v>
       </c>
       <c r="AD9">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AE9">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AF9">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AG9">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.64</v>
+        <v>1.14</v>
       </c>
       <c r="AK9">
-        <v>1.22</v>
+        <v>2.15</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="O10">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P10">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q10">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R10">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S10">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>3.54</v>
+        <v>3.32</v>
       </c>
       <c r="U10">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="V10">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
+        <v>1.11</v>
+      </c>
+      <c r="X10">
+        <v>1.03</v>
+      </c>
+      <c r="Y10">
+        <v>1.22</v>
+      </c>
+      <c r="Z10">
+        <v>4.2</v>
+      </c>
+      <c r="AA10">
+        <v>1.74</v>
+      </c>
+      <c r="AB10">
+        <v>2.05</v>
+      </c>
+      <c r="AC10">
+        <v>2.69</v>
+      </c>
+      <c r="AD10">
+        <v>1.44</v>
+      </c>
+      <c r="AE10">
         <v>1.14</v>
       </c>
-      <c r="X10">
-        <v>1.01</v>
-      </c>
-      <c r="Y10">
-        <v>1.14</v>
-      </c>
-      <c r="Z10">
-        <v>4.8</v>
-      </c>
-      <c r="AA10">
-        <v>1.56</v>
-      </c>
-      <c r="AB10">
-        <v>2.46</v>
-      </c>
-      <c r="AC10">
-        <v>2.3</v>
-      </c>
-      <c r="AD10">
-        <v>1.53</v>
-      </c>
-      <c r="AE10">
-        <v>1.23</v>
-      </c>
       <c r="AF10">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AG10">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK10">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.75</v>
+        <v>2.9</v>
       </c>
       <c r="O11">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P11">
-        <v>4.1</v>
+        <v>1.93</v>
       </c>
       <c r="Q11">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="R11">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T11">
-        <v>3.12</v>
+        <v>3.75</v>
       </c>
       <c r="U11">
-        <v>2.59</v>
+        <v>2.29</v>
       </c>
       <c r="V11">
+        <v>1.57</v>
+      </c>
+      <c r="W11">
+        <v>1.14</v>
+      </c>
+      <c r="X11">
+        <v>1.01</v>
+      </c>
+      <c r="Y11">
+        <v>1.17</v>
+      </c>
+      <c r="Z11">
+        <v>4.62</v>
+      </c>
+      <c r="AA11">
+        <v>1.54</v>
+      </c>
+      <c r="AB11">
+        <v>2.4</v>
+      </c>
+      <c r="AC11">
+        <v>2.4</v>
+      </c>
+      <c r="AD11">
+        <v>1.58</v>
+      </c>
+      <c r="AE11">
+        <v>1.2</v>
+      </c>
+      <c r="AF11">
+        <v>1.5</v>
+      </c>
+      <c r="AG11">
+        <v>2.5</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
         <v>1.44</v>
       </c>
-      <c r="W11">
-        <v>1.11</v>
-      </c>
-      <c r="X11">
-        <v>1.03</v>
-      </c>
-      <c r="Y11">
-        <v>1.2</v>
-      </c>
-      <c r="Z11">
-        <v>4.33</v>
-      </c>
-      <c r="AA11">
-        <v>1.74</v>
-      </c>
-      <c r="AB11">
-        <v>2.07</v>
-      </c>
-      <c r="AC11">
-        <v>2.69</v>
-      </c>
-      <c r="AD11">
-        <v>1.44</v>
-      </c>
-      <c r="AE11">
-        <v>1.14</v>
-      </c>
-      <c r="AF11">
-        <v>1.65</v>
-      </c>
-      <c r="AG11">
-        <v>2.08</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.19</v>
-      </c>
       <c r="AK11">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P12">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q12">
-        <v>3.29</v>
+        <v>4</v>
       </c>
       <c r="R12">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S12">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="U12">
-        <v>2.29</v>
+        <v>2.62</v>
       </c>
       <c r="V12">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="W12">
+        <v>1.1</v>
+      </c>
+      <c r="X12">
+        <v>1.03</v>
+      </c>
+      <c r="Y12">
+        <v>1.28</v>
+      </c>
+      <c r="Z12">
+        <v>3.69</v>
+      </c>
+      <c r="AA12">
+        <v>1.85</v>
+      </c>
+      <c r="AB12">
+        <v>1.95</v>
+      </c>
+      <c r="AC12">
+        <v>2.85</v>
+      </c>
+      <c r="AD12">
+        <v>1.39</v>
+      </c>
+      <c r="AE12">
         <v>1.14</v>
       </c>
-      <c r="X12">
-        <v>1.01</v>
-      </c>
-      <c r="Y12">
-        <v>1.17</v>
-      </c>
-      <c r="Z12">
-        <v>4.57</v>
-      </c>
-      <c r="AA12">
-        <v>1.55</v>
-      </c>
-      <c r="AB12">
-        <v>2.35</v>
-      </c>
-      <c r="AC12">
-        <v>2.39</v>
-      </c>
-      <c r="AD12">
-        <v>1.54</v>
-      </c>
-      <c r="AE12">
-        <v>1.2</v>
-      </c>
       <c r="AF12">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AG12">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AK12">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="O13">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="P13">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="Q13">
-        <v>4.45</v>
+        <v>4.53</v>
       </c>
       <c r="R13">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="S13">
         <v>1.2</v>
       </c>
       <c r="T13">
-        <v>3.96</v>
+        <v>3.75</v>
       </c>
       <c r="U13">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V13">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="W13">
         <v>1.17</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z13">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA13">
         <v>1.4</v>
       </c>
       <c r="AB13">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC13">
         <v>2.1</v>
       </c>
       <c r="AD13">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AE13">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF13">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG13">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.14</v>
       </c>
       <c r="AK13">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,28 +2591,28 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="O14">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="P14">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="Q14">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="R14">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="S14">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="T14">
         <v>2.4</v>
       </c>
       <c r="U14">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="V14">
         <v>1.25</v>
@@ -2627,28 +2627,28 @@
         <v>1.53</v>
       </c>
       <c r="Z14">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="AA14">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="AB14">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC14">
-        <v>4.86</v>
+        <v>4.9</v>
       </c>
       <c r="AD14">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE14">
         <v>1.02</v>
       </c>
       <c r="AF14">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG14">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK14">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2917,80 +2917,80 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P16">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="Q16">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R16">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="S16">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="T16">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U16">
-        <v>2.59</v>
+        <v>2.78</v>
       </c>
       <c r="V16">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X16">
         <v>1</v>
       </c>
       <c r="Y16">
+        <v>1.32</v>
+      </c>
+      <c r="Z16">
+        <v>3.16</v>
+      </c>
+      <c r="AA16">
+        <v>2.07</v>
+      </c>
+      <c r="AB16">
+        <v>1.82</v>
+      </c>
+      <c r="AC16">
+        <v>3.36</v>
+      </c>
+      <c r="AD16">
+        <v>1.29</v>
+      </c>
+      <c r="AE16">
+        <v>1.07</v>
+      </c>
+      <c r="AF16">
+        <v>1.83</v>
+      </c>
+      <c r="AG16">
+        <v>1.91</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
         <v>1.28</v>
       </c>
-      <c r="Z16">
-        <v>3.42</v>
-      </c>
-      <c r="AA16">
-        <v>1.9</v>
-      </c>
-      <c r="AB16">
-        <v>1.91</v>
-      </c>
-      <c r="AC16">
-        <v>3.07</v>
-      </c>
-      <c r="AD16">
-        <v>1.34</v>
-      </c>
-      <c r="AE16">
-        <v>1.08</v>
-      </c>
-      <c r="AF16">
-        <v>1.67</v>
-      </c>
-      <c r="AG16">
-        <v>2.1</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.3</v>
-      </c>
       <c r="AK16">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3445,10 +3445,10 @@
         <v>2.7</v>
       </c>
       <c r="AA19">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AB19">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC19">
         <v>4.4</v>
@@ -3460,10 +3460,10 @@
         <v>1.01</v>
       </c>
       <c r="AF19">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG19">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3572,28 +3572,28 @@
         <v>1.78</v>
       </c>
       <c r="O20">
-        <v>3.56</v>
+        <v>3.68</v>
       </c>
       <c r="P20">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="Q20">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R20">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T20">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="U20">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="V20">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W20">
         <v>1.03</v>
@@ -3602,31 +3602,31 @@
         <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="Z20">
-        <v>2.51</v>
+        <v>2.9</v>
       </c>
       <c r="AA20">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AB20">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AC20">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="AD20">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE20">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF20">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG20">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK20">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL20">
         <v>0</v>

--- a/jogos_2026-10-02.xlsx
+++ b/jogos_2026-10-02.xlsx
@@ -775,13 +775,13 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -790,11 +790,11 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,12 +859,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67", "90+9"]</t>
         </is>
       </c>
       <c r="AJ3">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -1104,13 +1104,13 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,26 +1264,26 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["56", "68", "90", "90+5"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["1"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,130 +1427,130 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P7">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="Q7">
-        <v>3.56</v>
+        <v>3.96</v>
       </c>
       <c r="R7">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="S7">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T7">
-        <v>3.36</v>
+        <v>3.65</v>
       </c>
       <c r="U7">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V7">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="W7">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z7">
-        <v>5.02</v>
+        <v>5.6</v>
       </c>
       <c r="AA7">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB7">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="AC7">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="AD7">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AE7">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AF7">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AG7">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["88"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["26", "67"]</t>
         </is>
       </c>
       <c r="AJ7">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AK7">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1581,66 +1581,66 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
-        <v>2.87</v>
+        <v>1.65</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P8">
-        <v>2.13</v>
+        <v>4</v>
       </c>
       <c r="Q8">
-        <v>3.56</v>
+        <v>2.1</v>
       </c>
       <c r="R8">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="S8">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T8">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="U8">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="V8">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="W8">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X8">
         <v>1.01</v>
@@ -1649,22 +1649,22 @@
         <v>1.16</v>
       </c>
       <c r="Z8">
-        <v>4.61</v>
+        <v>4.8</v>
       </c>
       <c r="AA8">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AB8">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="AC8">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AD8">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="AE8">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AF8">
         <v>1.55</v>
@@ -1674,46 +1674,46 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "16", "40", "81"]</t>
         </is>
       </c>
       <c r="AJ8">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK8">
-        <v>1.33</v>
+        <v>2.15</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1744,139 +1744,139 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="O9">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P9">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Q9">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="R9">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S9">
+        <v>1.3</v>
+      </c>
+      <c r="T9">
+        <v>3.32</v>
+      </c>
+      <c r="U9">
+        <v>2.6</v>
+      </c>
+      <c r="V9">
+        <v>1.44</v>
+      </c>
+      <c r="W9">
+        <v>1.11</v>
+      </c>
+      <c r="X9">
+        <v>1.03</v>
+      </c>
+      <c r="Y9">
         <v>1.22</v>
       </c>
-      <c r="T9">
-        <v>3.54</v>
-      </c>
-      <c r="U9">
-        <v>2.2</v>
-      </c>
-      <c r="V9">
-        <v>1.62</v>
-      </c>
-      <c r="W9">
+      <c r="Z9">
+        <v>4.2</v>
+      </c>
+      <c r="AA9">
+        <v>1.74</v>
+      </c>
+      <c r="AB9">
+        <v>2.05</v>
+      </c>
+      <c r="AC9">
+        <v>2.69</v>
+      </c>
+      <c r="AD9">
+        <v>1.44</v>
+      </c>
+      <c r="AE9">
         <v>1.14</v>
       </c>
-      <c r="X9">
-        <v>1.01</v>
-      </c>
-      <c r="Y9">
-        <v>1.16</v>
-      </c>
-      <c r="Z9">
-        <v>4.8</v>
-      </c>
-      <c r="AA9">
-        <v>1.56</v>
-      </c>
-      <c r="AB9">
-        <v>2.55</v>
-      </c>
-      <c r="AC9">
-        <v>2.3</v>
-      </c>
-      <c r="AD9">
-        <v>1.6</v>
-      </c>
-      <c r="AE9">
-        <v>1.25</v>
-      </c>
       <c r="AF9">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AG9">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "45+1", "89"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61", "65", "82"]</t>
         </is>
       </c>
       <c r="AJ9">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AK9">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1907,25 +1907,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -1935,111 +1935,111 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>1.75</v>
+        <v>2.9</v>
       </c>
       <c r="O10">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>4.1</v>
+        <v>1.93</v>
       </c>
       <c r="Q10">
+        <v>3</v>
+      </c>
+      <c r="R10">
         <v>2.28</v>
       </c>
-      <c r="R10">
+      <c r="S10">
+        <v>1.22</v>
+      </c>
+      <c r="T10">
+        <v>3.75</v>
+      </c>
+      <c r="U10">
+        <v>2.29</v>
+      </c>
+      <c r="V10">
+        <v>1.57</v>
+      </c>
+      <c r="W10">
+        <v>1.14</v>
+      </c>
+      <c r="X10">
+        <v>1.01</v>
+      </c>
+      <c r="Y10">
+        <v>1.17</v>
+      </c>
+      <c r="Z10">
+        <v>4.62</v>
+      </c>
+      <c r="AA10">
+        <v>1.54</v>
+      </c>
+      <c r="AB10">
         <v>2.4</v>
       </c>
-      <c r="S10">
-        <v>1.3</v>
-      </c>
-      <c r="T10">
-        <v>3.32</v>
-      </c>
-      <c r="U10">
-        <v>2.6</v>
-      </c>
-      <c r="V10">
+      <c r="AC10">
+        <v>2.4</v>
+      </c>
+      <c r="AD10">
+        <v>1.58</v>
+      </c>
+      <c r="AE10">
+        <v>1.2</v>
+      </c>
+      <c r="AF10">
+        <v>1.5</v>
+      </c>
+      <c r="AG10">
+        <v>2.5</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>["6", "38"]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>["33"]</t>
+        </is>
+      </c>
+      <c r="AJ10">
         <v>1.44</v>
       </c>
-      <c r="W10">
-        <v>1.11</v>
-      </c>
-      <c r="X10">
-        <v>1.03</v>
-      </c>
-      <c r="Y10">
-        <v>1.22</v>
-      </c>
-      <c r="Z10">
-        <v>4.2</v>
-      </c>
-      <c r="AA10">
-        <v>1.74</v>
-      </c>
-      <c r="AB10">
-        <v>2.05</v>
-      </c>
-      <c r="AC10">
-        <v>2.69</v>
-      </c>
-      <c r="AD10">
+      <c r="AK10">
+        <v>1.4</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>3</v>
+      </c>
+      <c r="AN10">
+        <v>4</v>
+      </c>
+      <c r="AO10">
+        <v>6</v>
+      </c>
+      <c r="AP10">
+        <v>11</v>
+      </c>
+      <c r="AQ10">
+        <v>0.9</v>
+      </c>
+      <c r="AR10">
         <v>1.44</v>
       </c>
-      <c r="AE10">
-        <v>1.14</v>
-      </c>
-      <c r="AF10">
-        <v>1.7</v>
-      </c>
-      <c r="AG10">
-        <v>2.05</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.18</v>
-      </c>
-      <c r="AK10">
-        <v>1.91</v>
-      </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>-1</v>
-      </c>
-      <c r="AN10">
-        <v>-1</v>
-      </c>
-      <c r="AO10">
-        <v>-1</v>
-      </c>
-      <c r="AP10">
-        <v>-1</v>
-      </c>
-      <c r="AQ10">
-        <v>0</v>
-      </c>
-      <c r="AR10">
-        <v>0</v>
-      </c>
       <c r="AS10">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2070,22 +2070,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2094,115 +2094,115 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P11">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q11">
+        <v>4</v>
+      </c>
+      <c r="R11">
+        <v>2.2</v>
+      </c>
+      <c r="S11">
+        <v>1.35</v>
+      </c>
+      <c r="T11">
         <v>3</v>
       </c>
-      <c r="R11">
-        <v>2.28</v>
-      </c>
-      <c r="S11">
+      <c r="U11">
+        <v>2.62</v>
+      </c>
+      <c r="V11">
+        <v>1.43</v>
+      </c>
+      <c r="W11">
+        <v>1.1</v>
+      </c>
+      <c r="X11">
+        <v>1.03</v>
+      </c>
+      <c r="Y11">
+        <v>1.28</v>
+      </c>
+      <c r="Z11">
+        <v>3.69</v>
+      </c>
+      <c r="AA11">
+        <v>1.85</v>
+      </c>
+      <c r="AB11">
+        <v>1.95</v>
+      </c>
+      <c r="AC11">
+        <v>2.85</v>
+      </c>
+      <c r="AD11">
+        <v>1.39</v>
+      </c>
+      <c r="AE11">
+        <v>1.14</v>
+      </c>
+      <c r="AF11">
+        <v>1.73</v>
+      </c>
+      <c r="AG11">
+        <v>2</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>["3"]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>["72", "79"]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>1.78</v>
+      </c>
+      <c r="AK11">
+        <v>1.18</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>5</v>
+      </c>
+      <c r="AN11">
+        <v>3</v>
+      </c>
+      <c r="AO11">
+        <v>9</v>
+      </c>
+      <c r="AP11">
+        <v>9</v>
+      </c>
+      <c r="AQ11">
+        <v>1.39</v>
+      </c>
+      <c r="AR11">
         <v>1.22</v>
       </c>
-      <c r="T11">
-        <v>3.75</v>
-      </c>
-      <c r="U11">
-        <v>2.29</v>
-      </c>
-      <c r="V11">
-        <v>1.57</v>
-      </c>
-      <c r="W11">
-        <v>1.14</v>
-      </c>
-      <c r="X11">
-        <v>1.01</v>
-      </c>
-      <c r="Y11">
-        <v>1.17</v>
-      </c>
-      <c r="Z11">
-        <v>4.62</v>
-      </c>
-      <c r="AA11">
-        <v>1.54</v>
-      </c>
-      <c r="AB11">
-        <v>2.4</v>
-      </c>
-      <c r="AC11">
-        <v>2.4</v>
-      </c>
-      <c r="AD11">
-        <v>1.58</v>
-      </c>
-      <c r="AE11">
-        <v>1.2</v>
-      </c>
-      <c r="AF11">
-        <v>1.5</v>
-      </c>
-      <c r="AG11">
-        <v>2.5</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.44</v>
-      </c>
-      <c r="AK11">
-        <v>1.4</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>-1</v>
-      </c>
-      <c r="AN11">
-        <v>-1</v>
-      </c>
-      <c r="AO11">
-        <v>-1</v>
-      </c>
-      <c r="AP11">
-        <v>-1</v>
-      </c>
-      <c r="AQ11">
-        <v>0</v>
-      </c>
-      <c r="AR11">
-        <v>0</v>
-      </c>
       <c r="AS11">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2218,158 +2218,158 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="O12">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="P12">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="Q12">
-        <v>4</v>
+        <v>4.53</v>
       </c>
       <c r="R12">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="S12">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="T12">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="U12">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="V12">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z12">
-        <v>3.69</v>
+        <v>5.75</v>
       </c>
       <c r="AA12">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="AB12">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AC12">
-        <v>2.85</v>
+        <v>2.1</v>
       </c>
       <c r="AD12">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="AE12">
+        <v>1.22</v>
+      </c>
+      <c r="AF12">
+        <v>1.57</v>
+      </c>
+      <c r="AG12">
+        <v>2.3</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>["13", "54"]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>["6", "44"]</t>
+        </is>
+      </c>
+      <c r="AJ12">
         <v>1.14</v>
       </c>
-      <c r="AF12">
-        <v>1.73</v>
-      </c>
-      <c r="AG12">
-        <v>2</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.78</v>
-      </c>
       <c r="AK12">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>31</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-10-02 15:45:00</t>
+          <t>2026-10-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -2381,108 +2381,108 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
-        <v>4.8</v>
+        <v>2.87</v>
       </c>
       <c r="O13">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P13">
-        <v>1.48</v>
+        <v>2.13</v>
       </c>
       <c r="Q13">
-        <v>4.53</v>
+        <v>3.56</v>
       </c>
       <c r="R13">
+        <v>2.47</v>
+      </c>
+      <c r="S13">
+        <v>1.29</v>
+      </c>
+      <c r="T13">
+        <v>3.42</v>
+      </c>
+      <c r="U13">
+        <v>2.38</v>
+      </c>
+      <c r="V13">
+        <v>1.53</v>
+      </c>
+      <c r="W13">
+        <v>1.12</v>
+      </c>
+      <c r="X13">
+        <v>1.01</v>
+      </c>
+      <c r="Y13">
+        <v>1.16</v>
+      </c>
+      <c r="Z13">
+        <v>4.61</v>
+      </c>
+      <c r="AA13">
+        <v>1.58</v>
+      </c>
+      <c r="AB13">
+        <v>2.18</v>
+      </c>
+      <c r="AC13">
         <v>2.49</v>
       </c>
-      <c r="S13">
-        <v>1.2</v>
-      </c>
-      <c r="T13">
-        <v>3.75</v>
-      </c>
-      <c r="U13">
-        <v>2</v>
-      </c>
-      <c r="V13">
-        <v>1.65</v>
-      </c>
-      <c r="W13">
-        <v>1.17</v>
-      </c>
-      <c r="X13">
-        <v>1.02</v>
-      </c>
-      <c r="Y13">
-        <v>1.15</v>
-      </c>
-      <c r="Z13">
-        <v>5.75</v>
-      </c>
-      <c r="AA13">
-        <v>1.4</v>
-      </c>
-      <c r="AB13">
-        <v>2.7</v>
-      </c>
-      <c r="AC13">
-        <v>2.1</v>
-      </c>
       <c r="AD13">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="AE13">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AF13">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG13">
         <v>2.3</v>
@@ -2494,45 +2494,45 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "34", "38", "88"]</t>
         </is>
       </c>
       <c r="AJ13">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-10-02 16:00:00</t>
+          <t>2026-10-02 16:15:00</t>
         </is>
       </c>
     </row>
@@ -2594,10 +2594,10 @@
         <v>1.98</v>
       </c>
       <c r="O14">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P14">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="Q14">
         <v>2.7</v>
@@ -2606,7 +2606,7 @@
         <v>1.91</v>
       </c>
       <c r="S14">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="T14">
         <v>2.4</v>
@@ -2633,7 +2633,7 @@
         <v>2.49</v>
       </c>
       <c r="AB14">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AC14">
         <v>4.9</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="O15">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="P15">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="Q15">
-        <v>3.25</v>
+        <v>2.77</v>
       </c>
       <c r="R15">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="S15">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="T15">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="U15">
-        <v>3.94</v>
+        <v>3.68</v>
       </c>
       <c r="V15">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W15">
         <v>1.04</v>
       </c>
       <c r="X15">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y15">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="Z15">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="AA15">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="AB15">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AC15">
-        <v>5.84</v>
+        <v>4.87</v>
       </c>
       <c r="AD15">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF15">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AG15">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK15">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3080,61 +3080,61 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O17">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P17">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="Q17">
         <v>2.5</v>
       </c>
       <c r="R17">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="S17">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="T17">
-        <v>2.58</v>
+        <v>2.51</v>
       </c>
       <c r="U17">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="V17">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z17">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AA17">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB17">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AC17">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="AD17">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE17">
         <v>1.1</v>
       </c>
       <c r="AF17">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AG17">
         <v>1.81</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK17">
         <v>1.75</v>
@@ -3243,22 +3243,22 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O18">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P18">
         <v>3.3</v>
       </c>
       <c r="Q18">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="R18">
         <v>2.2</v>
       </c>
       <c r="S18">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T18">
         <v>3.1</v>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>4.06</v>
+        <v>3.3</v>
       </c>
       <c r="O21">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="Q21">
-        <v>3.62</v>
+        <v>3.74</v>
       </c>
       <c r="R21">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="S21">
         <v>1.25</v>
@@ -3753,43 +3753,43 @@
         <v>3.6</v>
       </c>
       <c r="U21">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="V21">
         <v>1.57</v>
       </c>
       <c r="W21">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X21">
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z21">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AA21">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AB21">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AC21">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AD21">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE21">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF21">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AG21">
-        <v>2.29</v>
+        <v>2.05</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.22</v>
       </c>
       <c r="AK21">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AL21">
         <v>0</v>
